--- a/docs/APC40MKII_Electric_Zentropa_Lost_Buttons_Map.xlsx
+++ b/docs/APC40MKII_Electric_Zentropa_Lost_Buttons_Map.xlsx
@@ -13856,11 +13856,7 @@
       <c r="A5" s="71" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="72" t="inlineStr">
-        <is>
-          <t>1784313900056</t>
-        </is>
-      </c>
+      <c r="B5" s="72" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -13902,7 +13898,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>/composition/layers/56/clips/1/connect</t>
+          <t>/composition/layers/56/connectnextclip</t>
         </is>
       </c>
       <c r="M5" s="71" t="n">
@@ -13928,7 +13924,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>/composition/layers/56/clips/1/connect</t>
+          <t>/composition/layers/56/connectnextclip</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -13951,11 +13947,7 @@
       <c r="A6" s="71" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="72" t="inlineStr">
-        <is>
-          <t>1784313900001</t>
-        </is>
-      </c>
+      <c r="B6" s="72" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -13997,7 +13989,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>/composition/layers/1/clips/1/connect</t>
+          <t>/composition/layers/1/connectnextclip</t>
         </is>
       </c>
       <c r="M6" s="71" t="n">
@@ -14023,7 +14015,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>/composition/layers/1/clips/1/connect</t>
+          <t>/composition/layers/1/connectnextclip</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -14046,11 +14038,7 @@
       <c r="A7" s="71" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="72" t="inlineStr">
-        <is>
-          <t>1784313900042</t>
-        </is>
-      </c>
+      <c r="B7" s="72" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14092,7 +14080,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>/composition/layers/42/clips/1/connect</t>
+          <t>/composition/layers/42/connectnextclip</t>
         </is>
       </c>
       <c r="M7" s="71" t="n">
@@ -14118,7 +14106,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>/composition/layers/42/clips/1/connect</t>
+          <t>/composition/layers/42/connectnextclip</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -14141,11 +14129,7 @@
       <c r="A8" s="71" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="72" t="inlineStr">
-        <is>
-          <t>1784313900041</t>
-        </is>
-      </c>
+      <c r="B8" s="72" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14187,7 +14171,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>/composition/layers/41/clips/1/connect</t>
+          <t>/composition/layers/41/connectnextclip</t>
         </is>
       </c>
       <c r="M8" s="71" t="n">
@@ -14213,7 +14197,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>/composition/layers/41/clips/1/connect</t>
+          <t>/composition/layers/41/connectnextclip</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -14236,11 +14220,7 @@
       <c r="A9" s="71" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="72" t="inlineStr">
-        <is>
-          <t>1784313900007</t>
-        </is>
-      </c>
+      <c r="B9" s="72" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14282,7 +14262,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>/composition/layers/7/clips/1/connect</t>
+          <t>/composition/layers/7/connectnextclip</t>
         </is>
       </c>
       <c r="M9" s="71" t="n">
@@ -14308,7 +14288,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>/composition/layers/7/clips/1/connect</t>
+          <t>/composition/layers/7/connectnextclip</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -14331,11 +14311,7 @@
       <c r="A10" s="71" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="72" t="inlineStr">
-        <is>
-          <t>1784313900005</t>
-        </is>
-      </c>
+      <c r="B10" s="72" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14377,7 +14353,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>/composition/layers/5/clips/1/connect</t>
+          <t>/composition/layers/5/connectnextclip</t>
         </is>
       </c>
       <c r="M10" s="71" t="n">
@@ -14403,7 +14379,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>/composition/layers/5/clips/1/connect</t>
+          <t>/composition/layers/5/connectnextclip</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -14426,11 +14402,7 @@
       <c r="A11" s="71" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="72" t="inlineStr">
-        <is>
-          <t>1784313900046</t>
-        </is>
-      </c>
+      <c r="B11" s="72" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14472,7 +14444,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>/composition/layers/46/clips/1/connect</t>
+          <t>/composition/layers/46/connectnextclip</t>
         </is>
       </c>
       <c r="M11" s="71" t="n">
@@ -14498,7 +14470,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>/composition/layers/46/clips/1/connect</t>
+          <t>/composition/layers/46/connectnextclip</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -14521,11 +14493,7 @@
       <c r="A12" s="71" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="72" t="inlineStr">
-        <is>
-          <t>1784313900023</t>
-        </is>
-      </c>
+      <c r="B12" s="72" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14567,7 +14535,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>/composition/layers/23/clips/1/connect</t>
+          <t>/composition/layers/23/connectnextclip</t>
         </is>
       </c>
       <c r="M12" s="71" t="n">
@@ -14593,7 +14561,7 @@
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>/composition/layers/23/clips/1/connect</t>
+          <t>/composition/layers/23/connectnextclip</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -14616,11 +14584,7 @@
       <c r="A13" s="71" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="72" t="inlineStr">
-        <is>
-          <t>1784313900050</t>
-        </is>
-      </c>
+      <c r="B13" s="72" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14662,7 +14626,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>/composition/layers/50/clips/1/connect</t>
+          <t>/composition/layers/50/connectnextclip</t>
         </is>
       </c>
       <c r="M13" s="71" t="n">
@@ -14688,7 +14652,7 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>/composition/layers/50/clips/1/connect</t>
+          <t>/composition/layers/50/connectnextclip</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -14711,11 +14675,7 @@
       <c r="A14" s="71" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="72" t="inlineStr">
-        <is>
-          <t>1784313900024</t>
-        </is>
-      </c>
+      <c r="B14" s="72" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14757,7 +14717,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>/composition/layers/24/clips/1/connect</t>
+          <t>/composition/layers/24/connectnextclip</t>
         </is>
       </c>
       <c r="M14" s="71" t="n">
@@ -14783,7 +14743,7 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>/composition/layers/24/clips/1/connect</t>
+          <t>/composition/layers/24/connectnextclip</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -14806,11 +14766,7 @@
       <c r="A15" s="71" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="72" t="inlineStr">
-        <is>
-          <t>1784313900044</t>
-        </is>
-      </c>
+      <c r="B15" s="72" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14852,7 +14808,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>/composition/layers/44/clips/1/connect</t>
+          <t>/composition/layers/44/connectnextclip</t>
         </is>
       </c>
       <c r="M15" s="71" t="n">
@@ -14878,7 +14834,7 @@
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>/composition/layers/44/clips/1/connect</t>
+          <t>/composition/layers/44/connectnextclip</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -14901,11 +14857,7 @@
       <c r="A16" s="71" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="72" t="inlineStr">
-        <is>
-          <t>1784313900013</t>
-        </is>
-      </c>
+      <c r="B16" s="72" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -14947,7 +14899,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>/composition/layers/13/clips/1/connect</t>
+          <t>/composition/layers/13/connectnextclip</t>
         </is>
       </c>
       <c r="M16" s="71" t="n">
@@ -14973,7 +14925,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>/composition/layers/13/clips/1/connect</t>
+          <t>/composition/layers/13/connectnextclip</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -14996,11 +14948,7 @@
       <c r="A17" s="71" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="72" t="inlineStr">
-        <is>
-          <t>1784313900045</t>
-        </is>
-      </c>
+      <c r="B17" s="72" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15042,7 +14990,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>/composition/layers/45/clips/1/connect</t>
+          <t>/composition/layers/45/connectnextclip</t>
         </is>
       </c>
       <c r="M17" s="71" t="n">
@@ -15068,7 +15016,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>/composition/layers/45/clips/1/connect</t>
+          <t>/composition/layers/45/connectnextclip</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -15091,11 +15039,7 @@
       <c r="A18" s="71" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="72" t="inlineStr">
-        <is>
-          <t>1784313900061</t>
-        </is>
-      </c>
+      <c r="B18" s="72" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15137,7 +15081,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>/composition/layers/61/clips/1/connect</t>
+          <t>/composition/layers/61/connectnextclip</t>
         </is>
       </c>
       <c r="M18" s="71" t="n">
@@ -15163,7 +15107,7 @@
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>/composition/layers/61/clips/1/connect</t>
+          <t>/composition/layers/61/connectnextclip</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -15186,11 +15130,7 @@
       <c r="A19" s="71" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="72" t="inlineStr">
-        <is>
-          <t>1784313900040</t>
-        </is>
-      </c>
+      <c r="B19" s="72" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15232,7 +15172,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>/composition/layers/40/clips/1/connect</t>
+          <t>/composition/layers/40/connectnextclip</t>
         </is>
       </c>
       <c r="M19" s="71" t="n">
@@ -15258,7 +15198,7 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>/composition/layers/40/clips/1/connect</t>
+          <t>/composition/layers/40/connectnextclip</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -15281,11 +15221,7 @@
       <c r="A20" s="71" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="72" t="inlineStr">
-        <is>
-          <t>1784313900012</t>
-        </is>
-      </c>
+      <c r="B20" s="72" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15327,7 +15263,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>/composition/layers/12/clips/1/connect</t>
+          <t>/composition/layers/12/connectnextclip</t>
         </is>
       </c>
       <c r="M20" s="71" t="n">
@@ -15353,7 +15289,7 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>/composition/layers/12/clips/1/connect</t>
+          <t>/composition/layers/12/connectnextclip</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -15376,11 +15312,7 @@
       <c r="A21" s="71" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="72" t="inlineStr">
-        <is>
-          <t>1784313900047</t>
-        </is>
-      </c>
+      <c r="B21" s="72" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15422,7 +15354,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>/composition/layers/47/clips/1/connect</t>
+          <t>/composition/layers/47/connectnextclip</t>
         </is>
       </c>
       <c r="M21" s="71" t="n">
@@ -15448,7 +15380,7 @@
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>/composition/layers/47/clips/1/connect</t>
+          <t>/composition/layers/47/connectnextclip</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -15471,11 +15403,7 @@
       <c r="A22" s="71" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="72" t="inlineStr">
-        <is>
-          <t>1784313900051</t>
-        </is>
-      </c>
+      <c r="B22" s="72" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15517,7 +15445,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>/composition/layers/51/clips/1/connect</t>
+          <t>/composition/layers/51/connectnextclip</t>
         </is>
       </c>
       <c r="M22" s="71" t="n">
@@ -15543,7 +15471,7 @@
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>/composition/layers/51/clips/1/connect</t>
+          <t>/composition/layers/51/connectnextclip</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -15566,11 +15494,7 @@
       <c r="A23" s="71" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="72" t="inlineStr">
-        <is>
-          <t>1784313900055</t>
-        </is>
-      </c>
+      <c r="B23" s="72" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15612,7 +15536,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>/composition/layers/55/clips/1/connect</t>
+          <t>/composition/layers/55/connectnextclip</t>
         </is>
       </c>
       <c r="M23" s="71" t="n">
@@ -15638,7 +15562,7 @@
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>/composition/layers/55/clips/1/connect</t>
+          <t>/composition/layers/55/connectnextclip</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -15661,11 +15585,7 @@
       <c r="A24" s="71" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="72" t="inlineStr">
-        <is>
-          <t>1784313900027</t>
-        </is>
-      </c>
+      <c r="B24" s="72" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15707,7 +15627,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>/composition/layers/27/clips/1/connect</t>
+          <t>/composition/layers/27/connectnextclip</t>
         </is>
       </c>
       <c r="M24" s="71" t="n">
@@ -15733,7 +15653,7 @@
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>/composition/layers/27/clips/1/connect</t>
+          <t>/composition/layers/27/connectnextclip</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -15756,11 +15676,7 @@
       <c r="A25" s="71" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="72" t="inlineStr">
-        <is>
-          <t>1784313900057</t>
-        </is>
-      </c>
+      <c r="B25" s="72" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15802,7 +15718,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>/composition/layers/57/clips/1/connect</t>
+          <t>/composition/layers/57/connectnextclip</t>
         </is>
       </c>
       <c r="M25" s="71" t="n">
@@ -15828,7 +15744,7 @@
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>/composition/layers/57/clips/1/connect</t>
+          <t>/composition/layers/57/connectnextclip</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -15851,11 +15767,7 @@
       <c r="A26" s="71" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="72" t="inlineStr">
-        <is>
-          <t>1784313900039</t>
-        </is>
-      </c>
+      <c r="B26" s="72" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15897,7 +15809,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>/composition/layers/39/clips/1/connect</t>
+          <t>/composition/layers/39/connectnextclip</t>
         </is>
       </c>
       <c r="M26" s="71" t="n">
@@ -15923,7 +15835,7 @@
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>/composition/layers/39/clips/1/connect</t>
+          <t>/composition/layers/39/connectnextclip</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -15946,11 +15858,7 @@
       <c r="A27" s="71" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="72" t="inlineStr">
-        <is>
-          <t>1784313900049</t>
-        </is>
-      </c>
+      <c r="B27" s="72" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -15992,7 +15900,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>/composition/layers/49/clips/1/connect</t>
+          <t>/composition/layers/49/connectnextclip</t>
         </is>
       </c>
       <c r="M27" s="71" t="n">
@@ -16018,7 +15926,7 @@
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>/composition/layers/49/clips/1/connect</t>
+          <t>/composition/layers/49/connectnextclip</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -16041,11 +15949,7 @@
       <c r="A28" s="71" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="72" t="inlineStr">
-        <is>
-          <t>1784313900037</t>
-        </is>
-      </c>
+      <c r="B28" s="72" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16087,7 +15991,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>/composition/layers/37/clips/1/connect</t>
+          <t>/composition/layers/37/connectnextclip</t>
         </is>
       </c>
       <c r="M28" s="71" t="n">
@@ -16113,7 +16017,7 @@
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>/composition/layers/37/clips/1/connect</t>
+          <t>/composition/layers/37/connectnextclip</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -16136,11 +16040,7 @@
       <c r="A29" s="71" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="72" t="inlineStr">
-        <is>
-          <t>1784313900022</t>
-        </is>
-      </c>
+      <c r="B29" s="72" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16182,7 +16082,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>/composition/layers/22/clips/1/connect</t>
+          <t>/composition/layers/22/connectnextclip</t>
         </is>
       </c>
       <c r="M29" s="71" t="n">
@@ -16208,7 +16108,7 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>/composition/layers/22/clips/1/connect</t>
+          <t>/composition/layers/22/connectnextclip</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -16231,11 +16131,7 @@
       <c r="A30" s="71" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="72" t="inlineStr">
-        <is>
-          <t>1784313900032</t>
-        </is>
-      </c>
+      <c r="B30" s="72" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16277,7 +16173,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>/composition/layers/32/clips/1/connect</t>
+          <t>/composition/layers/32/connectnextclip</t>
         </is>
       </c>
       <c r="M30" s="71" t="n">
@@ -16303,7 +16199,7 @@
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>/composition/layers/32/clips/1/connect</t>
+          <t>/composition/layers/32/connectnextclip</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -16326,11 +16222,7 @@
       <c r="A31" s="71" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="72" t="inlineStr">
-        <is>
-          <t>1784313900031</t>
-        </is>
-      </c>
+      <c r="B31" s="72" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16372,7 +16264,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>/composition/layers/31/clips/1/connect</t>
+          <t>/composition/layers/31/connectnextclip</t>
         </is>
       </c>
       <c r="M31" s="71" t="n">
@@ -16398,7 +16290,7 @@
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>/composition/layers/31/clips/1/connect</t>
+          <t>/composition/layers/31/connectnextclip</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -16421,11 +16313,7 @@
       <c r="A32" s="71" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="72" t="inlineStr">
-        <is>
-          <t>1784313900019</t>
-        </is>
-      </c>
+      <c r="B32" s="72" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16467,7 +16355,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>/composition/layers/19/clips/1/connect</t>
+          <t>/composition/layers/19/connectnextclip</t>
         </is>
       </c>
       <c r="M32" s="71" t="n">
@@ -16493,7 +16381,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>/composition/layers/19/clips/1/connect</t>
+          <t>/composition/layers/19/connectnextclip</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -16516,11 +16404,7 @@
       <c r="A33" s="71" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="72" t="inlineStr">
-        <is>
-          <t>1784313900054</t>
-        </is>
-      </c>
+      <c r="B33" s="72" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16562,7 +16446,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>/composition/layers/54/clips/1/connect</t>
+          <t>/composition/layers/54/connectnextclip</t>
         </is>
       </c>
       <c r="M33" s="71" t="n">
@@ -16588,7 +16472,7 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>/composition/layers/54/clips/1/connect</t>
+          <t>/composition/layers/54/connectnextclip</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -16611,11 +16495,7 @@
       <c r="A34" s="71" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="72" t="inlineStr">
-        <is>
-          <t>1784313900017</t>
-        </is>
-      </c>
+      <c r="B34" s="72" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16657,7 +16537,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>/composition/layers/17/clips/1/connect</t>
+          <t>/composition/layers/17/connectnextclip</t>
         </is>
       </c>
       <c r="M34" s="71" t="n">
@@ -16683,7 +16563,7 @@
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>/composition/layers/17/clips/1/connect</t>
+          <t>/composition/layers/17/connectnextclip</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -16706,11 +16586,7 @@
       <c r="A35" s="71" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="72" t="inlineStr">
-        <is>
-          <t>1784313900011</t>
-        </is>
-      </c>
+      <c r="B35" s="72" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16752,7 +16628,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>/composition/layers/11/clips/1/connect</t>
+          <t>/composition/layers/11/connectnextclip</t>
         </is>
       </c>
       <c r="M35" s="71" t="n">
@@ -16778,7 +16654,7 @@
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>/composition/layers/11/clips/1/connect</t>
+          <t>/composition/layers/11/connectnextclip</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -16801,11 +16677,7 @@
       <c r="A36" s="71" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="72" t="inlineStr">
-        <is>
-          <t>1784313900010</t>
-        </is>
-      </c>
+      <c r="B36" s="72" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16847,7 +16719,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>/composition/layers/10/clips/1/connect</t>
+          <t>/composition/layers/10/connectnextclip</t>
         </is>
       </c>
       <c r="M36" s="71" t="n">
@@ -16873,7 +16745,7 @@
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>/composition/layers/10/clips/1/connect</t>
+          <t>/composition/layers/10/connectnextclip</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -16896,11 +16768,7 @@
       <c r="A37" s="71" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="72" t="inlineStr">
-        <is>
-          <t>1784313900018</t>
-        </is>
-      </c>
+      <c r="B37" s="72" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -16942,7 +16810,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>/composition/layers/18/clips/1/connect</t>
+          <t>/composition/layers/18/connectnextclip</t>
         </is>
       </c>
       <c r="M37" s="71" t="n">
@@ -16968,7 +16836,7 @@
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>/composition/layers/18/clips/1/connect</t>
+          <t>/composition/layers/18/connectnextclip</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -16991,11 +16859,7 @@
       <c r="A38" s="71" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="72" t="inlineStr">
-        <is>
-          <t>1784313900002</t>
-        </is>
-      </c>
+      <c r="B38" s="72" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17037,7 +16901,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>/composition/layers/2/clips/1/connect</t>
+          <t>/composition/layers/2/connectnextclip</t>
         </is>
       </c>
       <c r="M38" s="71" t="n">
@@ -17063,7 +16927,7 @@
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>/composition/layers/2/clips/1/connect</t>
+          <t>/composition/layers/2/connectnextclip</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -17086,11 +16950,7 @@
       <c r="A39" s="71" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="72" t="inlineStr">
-        <is>
-          <t>1784313900048</t>
-        </is>
-      </c>
+      <c r="B39" s="72" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17132,7 +16992,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>/composition/layers/48/clips/1/connect</t>
+          <t>/composition/layers/48/connectnextclip</t>
         </is>
       </c>
       <c r="M39" s="71" t="n">
@@ -17158,7 +17018,7 @@
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>/composition/layers/48/clips/1/connect</t>
+          <t>/composition/layers/48/connectnextclip</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -17181,11 +17041,7 @@
       <c r="A40" s="71" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="72" t="inlineStr">
-        <is>
-          <t>1784313900064</t>
-        </is>
-      </c>
+      <c r="B40" s="72" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17227,7 +17083,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>/composition/layers/64/clips/1/connect</t>
+          <t>/composition/layers/64/connectnextclip</t>
         </is>
       </c>
       <c r="M40" s="71" t="n">
@@ -17253,7 +17109,7 @@
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>/composition/layers/64/clips/1/connect</t>
+          <t>/composition/layers/64/connectnextclip</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -17276,11 +17132,7 @@
       <c r="A41" s="71" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="72" t="inlineStr">
-        <is>
-          <t>1784313900015</t>
-        </is>
-      </c>
+      <c r="B41" s="72" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17322,7 +17174,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>/composition/layers/15/clips/1/connect</t>
+          <t>/composition/layers/15/connectnextclip</t>
         </is>
       </c>
       <c r="M41" s="71" t="n">
@@ -17348,7 +17200,7 @@
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>/composition/layers/15/clips/1/connect</t>
+          <t>/composition/layers/15/connectnextclip</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -17371,11 +17223,7 @@
       <c r="A42" s="71" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="72" t="inlineStr">
-        <is>
-          <t>1784313900009</t>
-        </is>
-      </c>
+      <c r="B42" s="72" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17417,7 +17265,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>/composition/layers/9/clips/1/connect</t>
+          <t>/composition/layers/9/connectnextclip</t>
         </is>
       </c>
       <c r="M42" s="71" t="n">
@@ -17443,7 +17291,7 @@
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>/composition/layers/9/clips/1/connect</t>
+          <t>/composition/layers/9/connectnextclip</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -17466,11 +17314,7 @@
       <c r="A43" s="71" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="72" t="inlineStr">
-        <is>
-          <t>1784313900021</t>
-        </is>
-      </c>
+      <c r="B43" s="72" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17512,7 +17356,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>/composition/layers/21/clips/1/connect</t>
+          <t>/composition/layers/21/connectnextclip</t>
         </is>
       </c>
       <c r="M43" s="71" t="n">
@@ -17538,7 +17382,7 @@
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>/composition/layers/21/clips/1/connect</t>
+          <t>/composition/layers/21/connectnextclip</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
@@ -17561,11 +17405,7 @@
       <c r="A44" s="71" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="72" t="inlineStr">
-        <is>
-          <t>1784313900030</t>
-        </is>
-      </c>
+      <c r="B44" s="72" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17607,7 +17447,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>/composition/layers/30/clips/1/connect</t>
+          <t>/composition/layers/30/connectnextclip</t>
         </is>
       </c>
       <c r="M44" s="71" t="n">
@@ -17633,7 +17473,7 @@
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>/composition/layers/30/clips/1/connect</t>
+          <t>/composition/layers/30/connectnextclip</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -17656,11 +17496,7 @@
       <c r="A45" s="71" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="72" t="inlineStr">
-        <is>
-          <t>1784313900026</t>
-        </is>
-      </c>
+      <c r="B45" s="72" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17702,7 +17538,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>/composition/layers/26/clips/1/connect</t>
+          <t>/composition/layers/26/connectnextclip</t>
         </is>
       </c>
       <c r="M45" s="71" t="n">
@@ -17728,7 +17564,7 @@
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>/composition/layers/26/clips/1/connect</t>
+          <t>/composition/layers/26/connectnextclip</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -17751,11 +17587,7 @@
       <c r="A46" s="71" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="72" t="inlineStr">
-        <is>
-          <t>1784313900003</t>
-        </is>
-      </c>
+      <c r="B46" s="72" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17797,7 +17629,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>/composition/layers/3/clips/1/connect</t>
+          <t>/composition/layers/3/connectnextclip</t>
         </is>
       </c>
       <c r="M46" s="71" t="n">
@@ -17823,7 +17655,7 @@
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>/composition/layers/3/clips/1/connect</t>
+          <t>/composition/layers/3/connectnextclip</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -17846,11 +17678,7 @@
       <c r="A47" s="71" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="72" t="inlineStr">
-        <is>
-          <t>1784313900062</t>
-        </is>
-      </c>
+      <c r="B47" s="72" t="n"/>
       <c r="C47" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17892,7 +17720,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>/composition/layers/62/clips/1/connect</t>
+          <t>/composition/layers/62/connectnextclip</t>
         </is>
       </c>
       <c r="M47" s="71" t="n">
@@ -17918,7 +17746,7 @@
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>/composition/layers/62/clips/1/connect</t>
+          <t>/composition/layers/62/connectnextclip</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -17941,11 +17769,7 @@
       <c r="A48" s="71" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="72" t="inlineStr">
-        <is>
-          <t>1784313900034</t>
-        </is>
-      </c>
+      <c r="B48" s="72" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -17987,7 +17811,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>/composition/layers/34/clips/1/connect</t>
+          <t>/composition/layers/34/connectnextclip</t>
         </is>
       </c>
       <c r="M48" s="71" t="n">
@@ -18013,7 +17837,7 @@
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>/composition/layers/34/clips/1/connect</t>
+          <t>/composition/layers/34/connectnextclip</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -18036,11 +17860,7 @@
       <c r="A49" s="71" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="72" t="inlineStr">
-        <is>
-          <t>1784313900025</t>
-        </is>
-      </c>
+      <c r="B49" s="72" t="n"/>
       <c r="C49" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18082,7 +17902,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>/composition/layers/25/clips/1/connect</t>
+          <t>/composition/layers/25/connectnextclip</t>
         </is>
       </c>
       <c r="M49" s="71" t="n">
@@ -18108,7 +17928,7 @@
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>/composition/layers/25/clips/1/connect</t>
+          <t>/composition/layers/25/connectnextclip</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -18131,11 +17951,7 @@
       <c r="A50" s="71" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="72" t="inlineStr">
-        <is>
-          <t>1784313900014</t>
-        </is>
-      </c>
+      <c r="B50" s="72" t="n"/>
       <c r="C50" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18177,7 +17993,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>/composition/layers/14/clips/1/connect</t>
+          <t>/composition/layers/14/connectnextclip</t>
         </is>
       </c>
       <c r="M50" s="71" t="n">
@@ -18203,7 +18019,7 @@
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>/composition/layers/14/clips/1/connect</t>
+          <t>/composition/layers/14/connectnextclip</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
@@ -18226,11 +18042,7 @@
       <c r="A51" s="71" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="72" t="inlineStr">
-        <is>
-          <t>1784313900033</t>
-        </is>
-      </c>
+      <c r="B51" s="72" t="n"/>
       <c r="C51" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18272,7 +18084,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>/composition/layers/33/clips/1/connect</t>
+          <t>/composition/layers/33/connectnextclip</t>
         </is>
       </c>
       <c r="M51" s="71" t="n">
@@ -18298,7 +18110,7 @@
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>/composition/layers/33/clips/1/connect</t>
+          <t>/composition/layers/33/connectnextclip</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
@@ -18321,11 +18133,7 @@
       <c r="A52" s="71" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="72" t="inlineStr">
-        <is>
-          <t>1784313900063</t>
-        </is>
-      </c>
+      <c r="B52" s="72" t="n"/>
       <c r="C52" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18367,7 +18175,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>/composition/layers/63/clips/1/connect</t>
+          <t>/composition/layers/63/connectnextclip</t>
         </is>
       </c>
       <c r="M52" s="71" t="n">
@@ -18393,7 +18201,7 @@
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>/composition/layers/63/clips/1/connect</t>
+          <t>/composition/layers/63/connectnextclip</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
@@ -18416,11 +18224,7 @@
       <c r="A53" s="71" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="72" t="inlineStr">
-        <is>
-          <t>1784313900016</t>
-        </is>
-      </c>
+      <c r="B53" s="72" t="n"/>
       <c r="C53" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18462,7 +18266,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>/composition/layers/16/clips/1/connect</t>
+          <t>/composition/layers/16/connectnextclip</t>
         </is>
       </c>
       <c r="M53" s="71" t="n">
@@ -18488,7 +18292,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>/composition/layers/16/clips/1/connect</t>
+          <t>/composition/layers/16/connectnextclip</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -18511,11 +18315,7 @@
       <c r="A54" s="71" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="72" t="inlineStr">
-        <is>
-          <t>1784313900029</t>
-        </is>
-      </c>
+      <c r="B54" s="72" t="n"/>
       <c r="C54" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18557,7 +18357,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>/composition/layers/29/clips/1/connect</t>
+          <t>/composition/layers/29/connectnextclip</t>
         </is>
       </c>
       <c r="M54" s="71" t="n">
@@ -18583,7 +18383,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>/composition/layers/29/clips/1/connect</t>
+          <t>/composition/layers/29/connectnextclip</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -18606,11 +18406,7 @@
       <c r="A55" s="71" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="72" t="inlineStr">
-        <is>
-          <t>1784313900020</t>
-        </is>
-      </c>
+      <c r="B55" s="72" t="n"/>
       <c r="C55" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18652,7 +18448,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>/composition/layers/20/clips/1/connect</t>
+          <t>/composition/layers/20/connectnextclip</t>
         </is>
       </c>
       <c r="M55" s="71" t="n">
@@ -18678,7 +18474,7 @@
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>/composition/layers/20/clips/1/connect</t>
+          <t>/composition/layers/20/connectnextclip</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
@@ -18701,11 +18497,7 @@
       <c r="A56" s="71" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="72" t="inlineStr">
-        <is>
-          <t>1784313900036</t>
-        </is>
-      </c>
+      <c r="B56" s="72" t="n"/>
       <c r="C56" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18747,7 +18539,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>/composition/layers/36/clips/1/connect</t>
+          <t>/composition/layers/36/connectnextclip</t>
         </is>
       </c>
       <c r="M56" s="71" t="n">
@@ -18773,7 +18565,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>/composition/layers/36/clips/1/connect</t>
+          <t>/composition/layers/36/connectnextclip</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -18796,11 +18588,7 @@
       <c r="A57" s="71" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="72" t="inlineStr">
-        <is>
-          <t>1784313900006</t>
-        </is>
-      </c>
+      <c r="B57" s="72" t="n"/>
       <c r="C57" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18842,7 +18630,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>/composition/layers/6/clips/1/connect</t>
+          <t>/composition/layers/6/connectnextclip</t>
         </is>
       </c>
       <c r="M57" s="71" t="n">
@@ -18868,7 +18656,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>/composition/layers/6/clips/1/connect</t>
+          <t>/composition/layers/6/connectnextclip</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -18891,11 +18679,7 @@
       <c r="A58" s="71" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="72" t="inlineStr">
-        <is>
-          <t>1784313900035</t>
-        </is>
-      </c>
+      <c r="B58" s="72" t="n"/>
       <c r="C58" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -18937,7 +18721,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>/composition/layers/35/clips/1/connect</t>
+          <t>/composition/layers/35/connectnextclip</t>
         </is>
       </c>
       <c r="M58" s="71" t="n">
@@ -18963,7 +18747,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>/composition/layers/35/clips/1/connect</t>
+          <t>/composition/layers/35/connectnextclip</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -18986,11 +18770,7 @@
       <c r="A59" s="71" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="72" t="inlineStr">
-        <is>
-          <t>1784313900008</t>
-        </is>
-      </c>
+      <c r="B59" s="72" t="n"/>
       <c r="C59" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19032,7 +18812,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>/composition/layers/8/clips/1/connect</t>
+          <t>/composition/layers/8/connectnextclip</t>
         </is>
       </c>
       <c r="M59" s="71" t="n">
@@ -19058,7 +18838,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>/composition/layers/8/clips/1/connect</t>
+          <t>/composition/layers/8/connectnextclip</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -19081,11 +18861,7 @@
       <c r="A60" s="71" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="72" t="inlineStr">
-        <is>
-          <t>1784313900043</t>
-        </is>
-      </c>
+      <c r="B60" s="72" t="n"/>
       <c r="C60" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19127,7 +18903,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>/composition/layers/43/clips/1/connect</t>
+          <t>/composition/layers/43/connectnextclip</t>
         </is>
       </c>
       <c r="M60" s="71" t="n">
@@ -19153,7 +18929,7 @@
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>/composition/layers/43/clips/1/connect</t>
+          <t>/composition/layers/43/connectnextclip</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
@@ -19176,11 +18952,7 @@
       <c r="A61" s="71" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="72" t="inlineStr">
-        <is>
-          <t>1784313900058</t>
-        </is>
-      </c>
+      <c r="B61" s="72" t="n"/>
       <c r="C61" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19222,7 +18994,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>/composition/layers/58/clips/1/connect</t>
+          <t>/composition/layers/58/connectnextclip</t>
         </is>
       </c>
       <c r="M61" s="71" t="n">
@@ -19248,7 +19020,7 @@
       </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>/composition/layers/58/clips/1/connect</t>
+          <t>/composition/layers/58/connectnextclip</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
@@ -19271,11 +19043,7 @@
       <c r="A62" s="71" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="72" t="inlineStr">
-        <is>
-          <t>1784313900059</t>
-        </is>
-      </c>
+      <c r="B62" s="72" t="n"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19317,7 +19085,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>/composition/layers/59/clips/1/connect</t>
+          <t>/composition/layers/59/connectnextclip</t>
         </is>
       </c>
       <c r="M62" s="71" t="n">
@@ -19343,7 +19111,7 @@
       </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>/composition/layers/59/clips/1/connect</t>
+          <t>/composition/layers/59/connectnextclip</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
@@ -19366,11 +19134,7 @@
       <c r="A63" s="71" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="72" t="inlineStr">
-        <is>
-          <t>1784313900053</t>
-        </is>
-      </c>
+      <c r="B63" s="72" t="n"/>
       <c r="C63" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19412,7 +19176,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>/composition/layers/53/clips/1/connect</t>
+          <t>/composition/layers/53/connectnextclip</t>
         </is>
       </c>
       <c r="M63" s="71" t="n">
@@ -19438,7 +19202,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>/composition/layers/53/clips/1/connect</t>
+          <t>/composition/layers/53/connectnextclip</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
@@ -19461,11 +19225,7 @@
       <c r="A64" s="71" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="72" t="inlineStr">
-        <is>
-          <t>1784313900052</t>
-        </is>
-      </c>
+      <c r="B64" s="72" t="n"/>
       <c r="C64" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19507,7 +19267,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>/composition/layers/52/clips/1/connect</t>
+          <t>/composition/layers/52/connectnextclip</t>
         </is>
       </c>
       <c r="M64" s="71" t="n">
@@ -19533,7 +19293,7 @@
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>/composition/layers/52/clips/1/connect</t>
+          <t>/composition/layers/52/connectnextclip</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
@@ -19556,11 +19316,7 @@
       <c r="A65" s="71" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="72" t="inlineStr">
-        <is>
-          <t>1784313900060</t>
-        </is>
-      </c>
+      <c r="B65" s="72" t="n"/>
       <c r="C65" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19602,7 +19358,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>/composition/layers/60/clips/1/connect</t>
+          <t>/composition/layers/60/connectnextclip</t>
         </is>
       </c>
       <c r="M65" s="71" t="n">
@@ -19628,7 +19384,7 @@
       </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>/composition/layers/60/clips/1/connect</t>
+          <t>/composition/layers/60/connectnextclip</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
@@ -19651,11 +19407,7 @@
       <c r="A66" s="71" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="72" t="inlineStr">
-        <is>
-          <t>1784313900139</t>
-        </is>
-      </c>
+      <c r="B66" s="72" t="n"/>
       <c r="C66" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19697,7 +19449,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>/composition/layers/139/clips/1/connect</t>
+          <t>/composition/layers/139/connectnextclip</t>
         </is>
       </c>
       <c r="M66" s="71" t="n">
@@ -19723,7 +19475,7 @@
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>/composition/layers/139/clips/1/connect</t>
+          <t>/composition/layers/139/connectnextclip</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
@@ -19746,11 +19498,7 @@
       <c r="A67" s="71" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="72" t="inlineStr">
-        <is>
-          <t>1784313900078</t>
-        </is>
-      </c>
+      <c r="B67" s="72" t="n"/>
       <c r="C67" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19792,7 +19540,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>/composition/layers/78/clips/1/connect</t>
+          <t>/composition/layers/78/connectnextclip</t>
         </is>
       </c>
       <c r="M67" s="71" t="n">
@@ -19818,7 +19566,7 @@
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>/composition/layers/78/clips/1/connect</t>
+          <t>/composition/layers/78/connectnextclip</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
@@ -19841,11 +19589,7 @@
       <c r="A68" s="71" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="72" t="inlineStr">
-        <is>
-          <t>1784313900135</t>
-        </is>
-      </c>
+      <c r="B68" s="72" t="n"/>
       <c r="C68" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19887,7 +19631,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>/composition/layers/135/clips/1/connect</t>
+          <t>/composition/layers/135/connectnextclip</t>
         </is>
       </c>
       <c r="M68" s="71" t="n">
@@ -19913,7 +19657,7 @@
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>/composition/layers/135/clips/1/connect</t>
+          <t>/composition/layers/135/connectnextclip</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
@@ -19936,11 +19680,7 @@
       <c r="A69" s="71" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="72" t="inlineStr">
-        <is>
-          <t>1784313900004</t>
-        </is>
-      </c>
+      <c r="B69" s="72" t="n"/>
       <c r="C69" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -19982,7 +19722,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>/composition/layers/4/clips/1/connect</t>
+          <t>/composition/layers/4/connectnextclip</t>
         </is>
       </c>
       <c r="M69" s="71" t="n">
@@ -20008,7 +19748,7 @@
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>/composition/layers/4/clips/1/connect</t>
+          <t>/composition/layers/4/connectnextclip</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
@@ -20031,11 +19771,7 @@
       <c r="A70" s="71" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="72" t="inlineStr">
-        <is>
-          <t>1784313901145</t>
-        </is>
-      </c>
+      <c r="B70" s="72" t="n"/>
       <c r="C70" t="inlineStr">
         <is>
           <t>wake</t>
@@ -20111,11 +19847,7 @@
       <c r="A71" s="71" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="72" t="inlineStr">
-        <is>
-          <t>1784313900145</t>
-        </is>
-      </c>
+      <c r="B71" s="72" t="n"/>
       <c r="C71" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -20157,7 +19889,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>/composition/layers/145/clips/1/video/opacity</t>
+          <t>/composition/layers/145/clips/1/connect</t>
         </is>
       </c>
       <c r="M71" s="71" t="n">
@@ -20187,7 +19919,12 @@
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>/composition/layers/145/clips/1/video/opacity</t>
+          <t>/composition/layers/145/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -20195,11 +19932,7 @@
       <c r="A72" s="71" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="72" t="inlineStr">
-        <is>
-          <t>1784313902145</t>
-        </is>
-      </c>
+      <c r="B72" s="72" t="n"/>
       <c r="C72" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -20241,7 +19974,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>/composition/layers/145/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/145/clips/1/connect</t>
         </is>
       </c>
       <c r="M72" s="71" t="n">
@@ -20271,7 +20004,12 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>/composition/layers/145/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/145/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -20279,11 +20017,7 @@
       <c r="A73" s="71" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="72" t="inlineStr">
-        <is>
-          <t>1784313901148</t>
-        </is>
-      </c>
+      <c r="B73" s="72" t="n"/>
       <c r="C73" t="inlineStr">
         <is>
           <t>wake</t>
@@ -20359,11 +20093,7 @@
       <c r="A74" s="71" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="72" t="inlineStr">
-        <is>
-          <t>1784313900148</t>
-        </is>
-      </c>
+      <c r="B74" s="72" t="n"/>
       <c r="C74" t="inlineStr">
         <is>
           <t>tempo_motion</t>
@@ -20405,7 +20135,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>/composition/layers/148/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/148/clips/1/connect</t>
         </is>
       </c>
       <c r="M74" s="71" t="n">
@@ -20431,7 +20161,12 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>/composition/layers/148/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/148/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -20439,11 +20174,7 @@
       <c r="A75" s="71" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="72" t="inlineStr">
-        <is>
-          <t>1784313900067</t>
-        </is>
-      </c>
+      <c r="B75" s="72" t="n"/>
       <c r="C75" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -20485,7 +20216,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>/composition/layers/67/clips/1/connect</t>
+          <t>/composition/layers/67/connectnextclip</t>
         </is>
       </c>
       <c r="M75" s="71" t="n">
@@ -20511,7 +20242,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>/composition/layers/67/clips/1/connect</t>
+          <t>/composition/layers/67/connectnextclip</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -20534,11 +20265,7 @@
       <c r="A76" s="71" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="72" t="inlineStr">
-        <is>
-          <t>1784313901094</t>
-        </is>
-      </c>
+      <c r="B76" s="72" t="n"/>
       <c r="C76" t="inlineStr">
         <is>
           <t>wake</t>
@@ -20614,11 +20341,7 @@
       <c r="A77" s="71" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="72" t="inlineStr">
-        <is>
-          <t>1784313900094</t>
-        </is>
-      </c>
+      <c r="B77" s="72" t="n"/>
       <c r="C77" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -20660,7 +20383,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>/composition/layers/94/clips/1/video/opacity</t>
+          <t>/composition/layers/94/clips/1/connect</t>
         </is>
       </c>
       <c r="M77" s="71" t="n">
@@ -20690,7 +20413,12 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>/composition/layers/94/clips/1/video/opacity</t>
+          <t>/composition/layers/94/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -20698,11 +20426,7 @@
       <c r="A78" s="71" t="n">
         <v>74</v>
       </c>
-      <c r="B78" s="72" t="inlineStr">
-        <is>
-          <t>1784313902094</t>
-        </is>
-      </c>
+      <c r="B78" s="72" t="n"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -20744,7 +20468,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>/composition/layers/94/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/94/clips/1/connect</t>
         </is>
       </c>
       <c r="M78" s="71" t="n">
@@ -20774,7 +20498,12 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>/composition/layers/94/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/94/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -20782,11 +20511,7 @@
       <c r="A79" s="71" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="72" t="inlineStr">
-        <is>
-          <t>1784313900070</t>
-        </is>
-      </c>
+      <c r="B79" s="72" t="n"/>
       <c r="C79" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -20828,7 +20553,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>/composition/layers/70/clips/1/connect</t>
+          <t>/composition/layers/70/connectnextclip</t>
         </is>
       </c>
       <c r="M79" s="71" t="n">
@@ -20854,7 +20579,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>/composition/layers/70/clips/1/connect</t>
+          <t>/composition/layers/70/connectnextclip</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -20877,11 +20602,7 @@
       <c r="A80" s="71" t="n">
         <v>76</v>
       </c>
-      <c r="B80" s="72" t="inlineStr">
-        <is>
-          <t>1784313900147</t>
-        </is>
-      </c>
+      <c r="B80" s="72" t="n"/>
       <c r="C80" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -20923,7 +20644,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>/composition/layers/147/clips/1/connect</t>
+          <t>/composition/layers/147/connectnextclip</t>
         </is>
       </c>
       <c r="M80" s="71" t="n">
@@ -20949,7 +20670,7 @@
       </c>
       <c r="U80" t="inlineStr">
         <is>
-          <t>/composition/layers/147/clips/1/connect</t>
+          <t>/composition/layers/147/connectnextclip</t>
         </is>
       </c>
       <c r="V80" t="inlineStr">
@@ -20972,11 +20693,7 @@
       <c r="A81" s="71" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="72" t="inlineStr">
-        <is>
-          <t>1784313900140</t>
-        </is>
-      </c>
+      <c r="B81" s="72" t="n"/>
       <c r="C81" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21018,7 +20735,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>/composition/layers/140/clips/1/connect</t>
+          <t>/composition/layers/140/connectnextclip</t>
         </is>
       </c>
       <c r="M81" s="71" t="n">
@@ -21044,7 +20761,7 @@
       </c>
       <c r="U81" t="inlineStr">
         <is>
-          <t>/composition/layers/140/clips/1/connect</t>
+          <t>/composition/layers/140/connectnextclip</t>
         </is>
       </c>
       <c r="V81" t="inlineStr">
@@ -21067,11 +20784,7 @@
       <c r="A82" s="71" t="n">
         <v>78</v>
       </c>
-      <c r="B82" s="72" t="inlineStr">
-        <is>
-          <t>1784313900082</t>
-        </is>
-      </c>
+      <c r="B82" s="72" t="n"/>
       <c r="C82" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21113,7 +20826,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>/composition/layers/82/clips/1/connect</t>
+          <t>/composition/layers/82/connectnextclip</t>
         </is>
       </c>
       <c r="M82" s="71" t="n">
@@ -21139,7 +20852,7 @@
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>/composition/layers/82/clips/1/connect</t>
+          <t>/composition/layers/82/connectnextclip</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -21162,11 +20875,7 @@
       <c r="A83" s="71" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="72" t="inlineStr">
-        <is>
-          <t>1784313900090</t>
-        </is>
-      </c>
+      <c r="B83" s="72" t="n"/>
       <c r="C83" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21208,7 +20917,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>/composition/layers/90/clips/1/connect</t>
+          <t>/composition/layers/90/connectnextclip</t>
         </is>
       </c>
       <c r="M83" s="71" t="n">
@@ -21234,7 +20943,7 @@
       </c>
       <c r="U83" t="inlineStr">
         <is>
-          <t>/composition/layers/90/clips/1/connect</t>
+          <t>/composition/layers/90/connectnextclip</t>
         </is>
       </c>
       <c r="V83" t="inlineStr">
@@ -21257,11 +20966,7 @@
       <c r="A84" s="71" t="n">
         <v>80</v>
       </c>
-      <c r="B84" s="72" t="inlineStr">
-        <is>
-          <t>1784313900137</t>
-        </is>
-      </c>
+      <c r="B84" s="72" t="n"/>
       <c r="C84" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21303,7 +21008,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>/composition/layers/137/clips/1/connect</t>
+          <t>/composition/layers/137/connectnextclip</t>
         </is>
       </c>
       <c r="M84" s="71" t="n">
@@ -21329,7 +21034,7 @@
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>/composition/layers/137/clips/1/connect</t>
+          <t>/composition/layers/137/connectnextclip</t>
         </is>
       </c>
       <c r="V84" t="inlineStr">
@@ -21352,11 +21057,7 @@
       <c r="A85" s="71" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="72" t="inlineStr">
-        <is>
-          <t>1784313900138</t>
-        </is>
-      </c>
+      <c r="B85" s="72" t="n"/>
       <c r="C85" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21398,7 +21099,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>/composition/layers/138/clips/1/connect</t>
+          <t>/composition/layers/138/connectnextclip</t>
         </is>
       </c>
       <c r="M85" s="71" t="n">
@@ -21424,7 +21125,7 @@
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>/composition/layers/138/clips/1/connect</t>
+          <t>/composition/layers/138/connectnextclip</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -21447,11 +21148,7 @@
       <c r="A86" s="71" t="n">
         <v>82</v>
       </c>
-      <c r="B86" s="72" t="inlineStr">
-        <is>
-          <t>1784313900072</t>
-        </is>
-      </c>
+      <c r="B86" s="72" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21493,7 +21190,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>/composition/layers/72/clips/1/connect</t>
+          <t>/composition/layers/72/connectnextclip</t>
         </is>
       </c>
       <c r="M86" s="71" t="n">
@@ -21519,7 +21216,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>/composition/layers/72/clips/1/connect</t>
+          <t>/composition/layers/72/connectnextclip</t>
         </is>
       </c>
       <c r="V86" t="inlineStr">
@@ -21542,11 +21239,7 @@
       <c r="A87" s="71" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="72" t="inlineStr">
-        <is>
-          <t>1784313900142</t>
-        </is>
-      </c>
+      <c r="B87" s="72" t="n"/>
       <c r="C87" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21588,7 +21281,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>/composition/layers/142/clips/1/connect</t>
+          <t>/composition/layers/142/connectnextclip</t>
         </is>
       </c>
       <c r="M87" s="71" t="n">
@@ -21614,7 +21307,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>/composition/layers/142/clips/1/connect</t>
+          <t>/composition/layers/142/connectnextclip</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
@@ -21637,11 +21330,7 @@
       <c r="A88" s="71" t="n">
         <v>84</v>
       </c>
-      <c r="B88" s="72" t="inlineStr">
-        <is>
-          <t>1784313900141</t>
-        </is>
-      </c>
+      <c r="B88" s="72" t="n"/>
       <c r="C88" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21683,7 +21372,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>/composition/layers/141/clips/1/connect</t>
+          <t>/composition/layers/141/connectnextclip</t>
         </is>
       </c>
       <c r="M88" s="71" t="n">
@@ -21709,7 +21398,7 @@
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>/composition/layers/141/clips/1/connect</t>
+          <t>/composition/layers/141/connectnextclip</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
@@ -21732,11 +21421,7 @@
       <c r="A89" s="71" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="72" t="inlineStr">
-        <is>
-          <t>1784313900092</t>
-        </is>
-      </c>
+      <c r="B89" s="72" t="n"/>
       <c r="C89" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21778,7 +21463,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>/composition/layers/92/clips/1/connect</t>
+          <t>/composition/layers/92/connectnextclip</t>
         </is>
       </c>
       <c r="M89" s="71" t="n">
@@ -21804,7 +21489,7 @@
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>/composition/layers/92/clips/1/connect</t>
+          <t>/composition/layers/92/connectnextclip</t>
         </is>
       </c>
       <c r="V89" t="inlineStr">
@@ -21827,11 +21512,7 @@
       <c r="A90" s="71" t="n">
         <v>86</v>
       </c>
-      <c r="B90" s="72" t="inlineStr">
-        <is>
-          <t>1784313900071</t>
-        </is>
-      </c>
+      <c r="B90" s="72" t="n"/>
       <c r="C90" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21873,7 +21554,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>/composition/layers/71/clips/1/connect</t>
+          <t>/composition/layers/71/connectnextclip</t>
         </is>
       </c>
       <c r="M90" s="71" t="n">
@@ -21899,7 +21580,7 @@
       </c>
       <c r="U90" t="inlineStr">
         <is>
-          <t>/composition/layers/71/clips/1/connect</t>
+          <t>/composition/layers/71/connectnextclip</t>
         </is>
       </c>
       <c r="V90" t="inlineStr">
@@ -21922,11 +21603,7 @@
       <c r="A91" s="71" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="72" t="inlineStr">
-        <is>
-          <t>1784313900038</t>
-        </is>
-      </c>
+      <c r="B91" s="72" t="n"/>
       <c r="C91" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -21968,7 +21645,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>/composition/layers/38/clips/1/connect</t>
+          <t>/composition/layers/38/connectnextclip</t>
         </is>
       </c>
       <c r="M91" s="71" t="n">
@@ -21994,7 +21671,7 @@
       </c>
       <c r="U91" t="inlineStr">
         <is>
-          <t>/composition/layers/38/clips/1/connect</t>
+          <t>/composition/layers/38/connectnextclip</t>
         </is>
       </c>
       <c r="V91" t="inlineStr">
@@ -22017,11 +21694,7 @@
       <c r="A92" s="71" t="n">
         <v>88</v>
       </c>
-      <c r="B92" s="72" t="inlineStr">
-        <is>
-          <t>1784313901144</t>
-        </is>
-      </c>
+      <c r="B92" s="72" t="n"/>
       <c r="C92" t="inlineStr">
         <is>
           <t>wake</t>
@@ -22097,11 +21770,7 @@
       <c r="A93" s="71" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="72" t="inlineStr">
-        <is>
-          <t>1784313900144</t>
-        </is>
-      </c>
+      <c r="B93" s="72" t="n"/>
       <c r="C93" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -22143,7 +21812,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>/composition/layers/144/clips/1/video/opacity</t>
+          <t>/composition/layers/144/clips/1/connect</t>
         </is>
       </c>
       <c r="M93" s="71" t="n">
@@ -22173,7 +21842,12 @@
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>/composition/layers/144/clips/1/video/opacity</t>
+          <t>/composition/layers/144/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -22181,11 +21855,7 @@
       <c r="A94" s="71" t="n">
         <v>90</v>
       </c>
-      <c r="B94" s="72" t="inlineStr">
-        <is>
-          <t>1784313902144</t>
-        </is>
-      </c>
+      <c r="B94" s="72" t="n"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>motion_x</t>
@@ -22227,7 +21897,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>/composition/layers/144/clips/1/video/effects/transform/positionx</t>
+          <t>/composition/layers/144/clips/1/connect</t>
         </is>
       </c>
       <c r="M94" s="71" t="n">
@@ -22257,7 +21927,12 @@
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>/composition/layers/144/clips/1/video/effects/transform/positionx</t>
+          <t>/composition/layers/144/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -22265,11 +21940,7 @@
       <c r="A95" s="71" t="n">
         <v>91</v>
       </c>
-      <c r="B95" s="72" t="inlineStr">
-        <is>
-          <t>1784313901143</t>
-        </is>
-      </c>
+      <c r="B95" s="72" t="n"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>wake</t>
@@ -22345,11 +22016,7 @@
       <c r="A96" s="71" t="n">
         <v>92</v>
       </c>
-      <c r="B96" s="72" t="inlineStr">
-        <is>
-          <t>1784313900143</t>
-        </is>
-      </c>
+      <c r="B96" s="72" t="n"/>
       <c r="C96" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -22391,7 +22058,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>/composition/layers/143/clips/1/video/opacity</t>
+          <t>/composition/layers/143/clips/1/connect</t>
         </is>
       </c>
       <c r="M96" s="71" t="n">
@@ -22421,7 +22088,12 @@
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>/composition/layers/143/clips/1/video/opacity</t>
+          <t>/composition/layers/143/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -22429,11 +22101,7 @@
       <c r="A97" s="71" t="n">
         <v>93</v>
       </c>
-      <c r="B97" s="72" t="inlineStr">
-        <is>
-          <t>1784313902143</t>
-        </is>
-      </c>
+      <c r="B97" s="72" t="n"/>
       <c r="C97" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -22475,7 +22143,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>/composition/layers/143/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/143/clips/1/connect</t>
         </is>
       </c>
       <c r="M97" s="71" t="n">
@@ -22505,7 +22173,12 @@
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>/composition/layers/143/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/143/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -22513,11 +22186,7 @@
       <c r="A98" s="71" t="n">
         <v>94</v>
       </c>
-      <c r="B98" s="72" t="inlineStr">
-        <is>
-          <t>1784313900080</t>
-        </is>
-      </c>
+      <c r="B98" s="72" t="n"/>
       <c r="C98" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -22559,7 +22228,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>/composition/layers/80/clips/1/connect</t>
+          <t>/composition/layers/80/connectnextclip</t>
         </is>
       </c>
       <c r="M98" s="71" t="n">
@@ -22585,7 +22254,7 @@
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>/composition/layers/80/clips/1/connect</t>
+          <t>/composition/layers/80/connectnextclip</t>
         </is>
       </c>
       <c r="V98" t="inlineStr">
@@ -22608,11 +22277,7 @@
       <c r="A99" s="71" t="n">
         <v>95</v>
       </c>
-      <c r="B99" s="72" t="inlineStr">
-        <is>
-          <t>1784313900028</t>
-        </is>
-      </c>
+      <c r="B99" s="72" t="n"/>
       <c r="C99" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -22654,7 +22319,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>/composition/layers/28/clips/1/connect</t>
+          <t>/composition/layers/28/connectnextclip</t>
         </is>
       </c>
       <c r="M99" s="71" t="n">
@@ -22680,7 +22345,7 @@
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>/composition/layers/28/clips/1/connect</t>
+          <t>/composition/layers/28/connectnextclip</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
@@ -22703,11 +22368,7 @@
       <c r="A100" s="71" t="n">
         <v>96</v>
       </c>
-      <c r="B100" s="72" t="inlineStr">
-        <is>
-          <t>1784313900079</t>
-        </is>
-      </c>
+      <c r="B100" s="72" t="n"/>
       <c r="C100" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -22749,7 +22410,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>/composition/layers/79/clips/1/connect</t>
+          <t>/composition/layers/79/connectnextclip</t>
         </is>
       </c>
       <c r="M100" s="71" t="n">
@@ -22775,7 +22436,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>/composition/layers/79/clips/1/connect</t>
+          <t>/composition/layers/79/connectnextclip</t>
         </is>
       </c>
       <c r="V100" t="inlineStr">
@@ -22798,11 +22459,7 @@
       <c r="A101" s="71" t="n">
         <v>97</v>
       </c>
-      <c r="B101" s="72" t="inlineStr">
-        <is>
-          <t>1784313900069</t>
-        </is>
-      </c>
+      <c r="B101" s="72" t="n"/>
       <c r="C101" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -22844,7 +22501,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>/composition/layers/69/clips/1/connect</t>
+          <t>/composition/layers/69/connectnextclip</t>
         </is>
       </c>
       <c r="M101" s="71" t="n">
@@ -22870,7 +22527,7 @@
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>/composition/layers/69/clips/1/connect</t>
+          <t>/composition/layers/69/connectnextclip</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
@@ -22893,11 +22550,7 @@
       <c r="A102" s="71" t="n">
         <v>98</v>
       </c>
-      <c r="B102" s="72" t="inlineStr">
-        <is>
-          <t>1784313900146</t>
-        </is>
-      </c>
+      <c r="B102" s="72" t="n"/>
       <c r="C102" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -22939,7 +22592,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>/composition/layers/146/clips/1/connect</t>
+          <t>/composition/layers/146/connectnextclip</t>
         </is>
       </c>
       <c r="M102" s="71" t="n">
@@ -22965,7 +22618,7 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>/composition/layers/146/clips/1/connect</t>
+          <t>/composition/layers/146/connectnextclip</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
@@ -22988,11 +22641,7 @@
       <c r="A103" s="71" t="n">
         <v>99</v>
       </c>
-      <c r="B103" s="72" t="inlineStr">
-        <is>
-          <t>1784313900077</t>
-        </is>
-      </c>
+      <c r="B103" s="72" t="n"/>
       <c r="C103" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23034,7 +22683,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>/composition/layers/77/clips/1/connect</t>
+          <t>/composition/layers/77/connectnextclip</t>
         </is>
       </c>
       <c r="M103" s="71" t="n">
@@ -23060,7 +22709,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>/composition/layers/77/clips/1/connect</t>
+          <t>/composition/layers/77/connectnextclip</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
@@ -23083,11 +22732,7 @@
       <c r="A104" s="71" t="n">
         <v>100</v>
       </c>
-      <c r="B104" s="72" t="inlineStr">
-        <is>
-          <t>1784313900073</t>
-        </is>
-      </c>
+      <c r="B104" s="72" t="n"/>
       <c r="C104" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23129,7 +22774,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>/composition/layers/73/clips/1/connect</t>
+          <t>/composition/layers/73/connectnextclip</t>
         </is>
       </c>
       <c r="M104" s="71" t="n">
@@ -23155,7 +22800,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>/composition/layers/73/clips/1/connect</t>
+          <t>/composition/layers/73/connectnextclip</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
@@ -23178,11 +22823,7 @@
       <c r="A105" s="71" t="n">
         <v>101</v>
       </c>
-      <c r="B105" s="72" t="inlineStr">
-        <is>
-          <t>1784313900087</t>
-        </is>
-      </c>
+      <c r="B105" s="72" t="n"/>
       <c r="C105" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23224,7 +22865,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>/composition/layers/87/clips/1/connect</t>
+          <t>/composition/layers/87/connectnextclip</t>
         </is>
       </c>
       <c r="M105" s="71" t="n">
@@ -23250,7 +22891,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>/composition/layers/87/clips/1/connect</t>
+          <t>/composition/layers/87/connectnextclip</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
@@ -23273,11 +22914,7 @@
       <c r="A106" s="71" t="n">
         <v>102</v>
       </c>
-      <c r="B106" s="72" t="inlineStr">
-        <is>
-          <t>1784313900136</t>
-        </is>
-      </c>
+      <c r="B106" s="72" t="n"/>
       <c r="C106" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23319,7 +22956,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>/composition/layers/136/clips/1/connect</t>
+          <t>/composition/layers/136/connectnextclip</t>
         </is>
       </c>
       <c r="M106" s="71" t="n">
@@ -23345,7 +22982,7 @@
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>/composition/layers/136/clips/1/connect</t>
+          <t>/composition/layers/136/connectnextclip</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
@@ -23368,11 +23005,7 @@
       <c r="A107" s="71" t="n">
         <v>103</v>
       </c>
-      <c r="B107" s="72" t="inlineStr">
-        <is>
-          <t>1784313900091</t>
-        </is>
-      </c>
+      <c r="B107" s="72" t="n"/>
       <c r="C107" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23414,7 +23047,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>/composition/layers/91/clips/1/connect</t>
+          <t>/composition/layers/91/connectnextclip</t>
         </is>
       </c>
       <c r="M107" s="71" t="n">
@@ -23440,7 +23073,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>/composition/layers/91/clips/1/connect</t>
+          <t>/composition/layers/91/connectnextclip</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
@@ -23463,11 +23096,7 @@
       <c r="A108" s="71" t="n">
         <v>104</v>
       </c>
-      <c r="B108" s="72" t="inlineStr">
-        <is>
-          <t>1784313900085</t>
-        </is>
-      </c>
+      <c r="B108" s="72" t="n"/>
       <c r="C108" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23509,7 +23138,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>/composition/layers/85/clips/1/connect</t>
+          <t>/composition/layers/85/connectnextclip</t>
         </is>
       </c>
       <c r="M108" s="71" t="n">
@@ -23535,7 +23164,7 @@
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>/composition/layers/85/clips/1/connect</t>
+          <t>/composition/layers/85/connectnextclip</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
@@ -23558,11 +23187,7 @@
       <c r="A109" s="71" t="n">
         <v>105</v>
       </c>
-      <c r="B109" s="72" t="inlineStr">
-        <is>
-          <t>1784313901099</t>
-        </is>
-      </c>
+      <c r="B109" s="72" t="n"/>
       <c r="C109" t="inlineStr">
         <is>
           <t>wake</t>
@@ -23638,11 +23263,7 @@
       <c r="A110" s="71" t="n">
         <v>106</v>
       </c>
-      <c r="B110" s="72" t="inlineStr">
-        <is>
-          <t>1784313900099</t>
-        </is>
-      </c>
+      <c r="B110" s="72" t="n"/>
       <c r="C110" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -23684,7 +23305,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>/composition/layers/99/clips/1/video/opacity</t>
+          <t>/composition/layers/99/clips/1/connect</t>
         </is>
       </c>
       <c r="M110" s="71" t="n">
@@ -23714,7 +23335,12 @@
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>/composition/layers/99/clips/1/video/opacity</t>
+          <t>/composition/layers/99/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -23722,11 +23348,7 @@
       <c r="A111" s="71" t="n">
         <v>107</v>
       </c>
-      <c r="B111" s="72" t="inlineStr">
-        <is>
-          <t>1784313902099</t>
-        </is>
-      </c>
+      <c r="B111" s="72" t="n"/>
       <c r="C111" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -23768,7 +23390,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>/composition/layers/99/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/99/clips/1/connect</t>
         </is>
       </c>
       <c r="M111" s="71" t="n">
@@ -23798,7 +23420,12 @@
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>/composition/layers/99/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/99/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -23806,11 +23433,7 @@
       <c r="A112" s="71" t="n">
         <v>108</v>
       </c>
-      <c r="B112" s="72" t="inlineStr">
-        <is>
-          <t>1784313900075</t>
-        </is>
-      </c>
+      <c r="B112" s="72" t="n"/>
       <c r="C112" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -23852,7 +23475,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>/composition/layers/75/clips/1/connect</t>
+          <t>/composition/layers/75/connectnextclip</t>
         </is>
       </c>
       <c r="M112" s="71" t="n">
@@ -23878,7 +23501,7 @@
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>/composition/layers/75/clips/1/connect</t>
+          <t>/composition/layers/75/connectnextclip</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
@@ -23901,11 +23524,7 @@
       <c r="A113" s="71" t="n">
         <v>109</v>
       </c>
-      <c r="B113" s="72" t="inlineStr">
-        <is>
-          <t>1784313901109</t>
-        </is>
-      </c>
+      <c r="B113" s="72" t="n"/>
       <c r="C113" t="inlineStr">
         <is>
           <t>wake</t>
@@ -23981,11 +23600,7 @@
       <c r="A114" s="71" t="n">
         <v>110</v>
       </c>
-      <c r="B114" s="72" t="inlineStr">
-        <is>
-          <t>1784313900109</t>
-        </is>
-      </c>
+      <c r="B114" s="72" t="n"/>
       <c r="C114" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -24027,7 +23642,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>/composition/layers/109/clips/1/video/opacity</t>
+          <t>/composition/layers/109/clips/1/connect</t>
         </is>
       </c>
       <c r="M114" s="71" t="n">
@@ -24057,7 +23672,12 @@
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>/composition/layers/109/clips/1/video/opacity</t>
+          <t>/composition/layers/109/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -24065,11 +23685,7 @@
       <c r="A115" s="71" t="n">
         <v>111</v>
       </c>
-      <c r="B115" s="72" t="inlineStr">
-        <is>
-          <t>1784313902109</t>
-        </is>
-      </c>
+      <c r="B115" s="72" t="n"/>
       <c r="C115" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -24111,7 +23727,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>/composition/layers/109/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/109/clips/1/connect</t>
         </is>
       </c>
       <c r="M115" s="71" t="n">
@@ -24141,7 +23757,12 @@
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>/composition/layers/109/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/109/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -24149,11 +23770,7 @@
       <c r="A116" s="71" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="72" t="inlineStr">
-        <is>
-          <t>1784313900120</t>
-        </is>
-      </c>
+      <c r="B116" s="72" t="n"/>
       <c r="C116" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -24195,7 +23812,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>/composition/layers/120/clips/1/connect</t>
+          <t>/composition/layers/120/connectnextclip</t>
         </is>
       </c>
       <c r="M116" s="71" t="n">
@@ -24221,7 +23838,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>/composition/layers/120/clips/1/connect</t>
+          <t>/composition/layers/120/connectnextclip</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
@@ -24244,11 +23861,7 @@
       <c r="A117" s="71" t="n">
         <v>113</v>
       </c>
-      <c r="B117" s="72" t="inlineStr">
-        <is>
-          <t>1784313901106</t>
-        </is>
-      </c>
+      <c r="B117" s="72" t="n"/>
       <c r="C117" t="inlineStr">
         <is>
           <t>wake</t>
@@ -24324,11 +23937,7 @@
       <c r="A118" s="71" t="n">
         <v>114</v>
       </c>
-      <c r="B118" s="72" t="inlineStr">
-        <is>
-          <t>1784313900106</t>
-        </is>
-      </c>
+      <c r="B118" s="72" t="n"/>
       <c r="C118" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -24370,7 +23979,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>/composition/layers/106/clips/1/video/opacity</t>
+          <t>/composition/layers/106/clips/1/connect</t>
         </is>
       </c>
       <c r="M118" s="71" t="n">
@@ -24400,7 +24009,12 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>/composition/layers/106/clips/1/video/opacity</t>
+          <t>/composition/layers/106/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -24408,11 +24022,7 @@
       <c r="A119" s="71" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="72" t="inlineStr">
-        <is>
-          <t>1784313902106</t>
-        </is>
-      </c>
+      <c r="B119" s="72" t="n"/>
       <c r="C119" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -24454,7 +24064,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>/composition/layers/106/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/106/clips/1/connect</t>
         </is>
       </c>
       <c r="M119" s="71" t="n">
@@ -24484,7 +24094,12 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>/composition/layers/106/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/106/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -24492,11 +24107,7 @@
       <c r="A120" s="71" t="n">
         <v>116</v>
       </c>
-      <c r="B120" s="72" t="inlineStr">
-        <is>
-          <t>1784313900066</t>
-        </is>
-      </c>
+      <c r="B120" s="72" t="n"/>
       <c r="C120" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -24538,7 +24149,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>/composition/layers/66/clips/1/connect</t>
+          <t>/composition/layers/66/connectnextclip</t>
         </is>
       </c>
       <c r="M120" s="71" t="n">
@@ -24564,7 +24175,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>/composition/layers/66/clips/1/connect</t>
+          <t>/composition/layers/66/connectnextclip</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
@@ -24587,11 +24198,7 @@
       <c r="A121" s="71" t="n">
         <v>117</v>
       </c>
-      <c r="B121" s="72" t="inlineStr">
-        <is>
-          <t>1784313900083</t>
-        </is>
-      </c>
+      <c r="B121" s="72" t="n"/>
       <c r="C121" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -24633,7 +24240,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>/composition/layers/83/clips/1/connect</t>
+          <t>/composition/layers/83/connectnextclip</t>
         </is>
       </c>
       <c r="M121" s="71" t="n">
@@ -24659,7 +24266,7 @@
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>/composition/layers/83/clips/1/connect</t>
+          <t>/composition/layers/83/connectnextclip</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
@@ -24682,11 +24289,7 @@
       <c r="A122" s="71" t="n">
         <v>118</v>
       </c>
-      <c r="B122" s="72" t="inlineStr">
-        <is>
-          <t>1784313901114</t>
-        </is>
-      </c>
+      <c r="B122" s="72" t="n"/>
       <c r="C122" t="inlineStr">
         <is>
           <t>wake</t>
@@ -24762,11 +24365,7 @@
       <c r="A123" s="71" t="n">
         <v>119</v>
       </c>
-      <c r="B123" s="72" t="inlineStr">
-        <is>
-          <t>1784313900114</t>
-        </is>
-      </c>
+      <c r="B123" s="72" t="n"/>
       <c r="C123" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -24808,7 +24407,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>/composition/layers/114/clips/1/video/opacity</t>
+          <t>/composition/layers/114/clips/1/connect</t>
         </is>
       </c>
       <c r="M123" s="71" t="n">
@@ -24838,7 +24437,12 @@
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>/composition/layers/114/clips/1/video/opacity</t>
+          <t>/composition/layers/114/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -24846,11 +24450,7 @@
       <c r="A124" s="71" t="n">
         <v>120</v>
       </c>
-      <c r="B124" s="72" t="inlineStr">
-        <is>
-          <t>1784313902114</t>
-        </is>
-      </c>
+      <c r="B124" s="72" t="n"/>
       <c r="C124" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -24892,7 +24492,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>/composition/layers/114/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/114/clips/1/connect</t>
         </is>
       </c>
       <c r="M124" s="71" t="n">
@@ -24922,7 +24522,12 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>/composition/layers/114/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/114/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -24930,11 +24535,7 @@
       <c r="A125" s="71" t="n">
         <v>121</v>
       </c>
-      <c r="B125" s="72" t="inlineStr">
-        <is>
-          <t>1784313900122</t>
-        </is>
-      </c>
+      <c r="B125" s="72" t="n"/>
       <c r="C125" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -24976,7 +24577,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>/composition/layers/122/clips/1/connect</t>
+          <t>/composition/layers/122/connectnextclip</t>
         </is>
       </c>
       <c r="M125" s="71" t="n">
@@ -25002,7 +24603,7 @@
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>/composition/layers/122/clips/1/connect</t>
+          <t>/composition/layers/122/connectnextclip</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
@@ -25025,11 +24626,7 @@
       <c r="A126" s="71" t="n">
         <v>122</v>
       </c>
-      <c r="B126" s="72" t="inlineStr">
-        <is>
-          <t>1784313900086</t>
-        </is>
-      </c>
+      <c r="B126" s="72" t="n"/>
       <c r="C126" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -25071,7 +24668,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>/composition/layers/86/clips/1/connect</t>
+          <t>/composition/layers/86/connectnextclip</t>
         </is>
       </c>
       <c r="M126" s="71" t="n">
@@ -25097,7 +24694,7 @@
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>/composition/layers/86/clips/1/connect</t>
+          <t>/composition/layers/86/connectnextclip</t>
         </is>
       </c>
       <c r="V126" t="inlineStr">
@@ -25120,11 +24717,7 @@
       <c r="A127" s="71" t="n">
         <v>123</v>
       </c>
-      <c r="B127" s="72" t="inlineStr">
-        <is>
-          <t>1784313901113</t>
-        </is>
-      </c>
+      <c r="B127" s="72" t="n"/>
       <c r="C127" t="inlineStr">
         <is>
           <t>wake</t>
@@ -25200,11 +24793,7 @@
       <c r="A128" s="71" t="n">
         <v>124</v>
       </c>
-      <c r="B128" s="72" t="inlineStr">
-        <is>
-          <t>1784313900113</t>
-        </is>
-      </c>
+      <c r="B128" s="72" t="n"/>
       <c r="C128" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -25246,7 +24835,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>/composition/layers/113/clips/1/video/opacity</t>
+          <t>/composition/layers/113/clips/1/connect</t>
         </is>
       </c>
       <c r="M128" s="71" t="n">
@@ -25276,7 +24865,12 @@
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>/composition/layers/113/clips/1/video/opacity</t>
+          <t>/composition/layers/113/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -25284,11 +24878,7 @@
       <c r="A129" s="71" t="n">
         <v>125</v>
       </c>
-      <c r="B129" s="72" t="inlineStr">
-        <is>
-          <t>1784313902113</t>
-        </is>
-      </c>
+      <c r="B129" s="72" t="n"/>
       <c r="C129" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -25330,7 +24920,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>/composition/layers/113/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/113/clips/1/connect</t>
         </is>
       </c>
       <c r="M129" s="71" t="n">
@@ -25360,7 +24950,12 @@
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>/composition/layers/113/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/113/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -25368,11 +24963,7 @@
       <c r="A130" s="71" t="n">
         <v>126</v>
       </c>
-      <c r="B130" s="72" t="inlineStr">
-        <is>
-          <t>1784313901104</t>
-        </is>
-      </c>
+      <c r="B130" s="72" t="n"/>
       <c r="C130" t="inlineStr">
         <is>
           <t>wake</t>
@@ -25448,11 +25039,7 @@
       <c r="A131" s="71" t="n">
         <v>127</v>
       </c>
-      <c r="B131" s="72" t="inlineStr">
-        <is>
-          <t>1784313900104</t>
-        </is>
-      </c>
+      <c r="B131" s="72" t="n"/>
       <c r="C131" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -25494,7 +25081,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>/composition/layers/104/clips/1/video/opacity</t>
+          <t>/composition/layers/104/clips/1/connect</t>
         </is>
       </c>
       <c r="M131" s="71" t="n">
@@ -25524,7 +25111,12 @@
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>/composition/layers/104/clips/1/video/opacity</t>
+          <t>/composition/layers/104/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -25532,11 +25124,7 @@
       <c r="A132" s="71" t="n">
         <v>128</v>
       </c>
-      <c r="B132" s="72" t="inlineStr">
-        <is>
-          <t>1784313902104</t>
-        </is>
-      </c>
+      <c r="B132" s="72" t="n"/>
       <c r="C132" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -25578,7 +25166,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>/composition/layers/104/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/104/clips/1/connect</t>
         </is>
       </c>
       <c r="M132" s="71" t="n">
@@ -25608,7 +25196,12 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>/composition/layers/104/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/104/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -25616,11 +25209,7 @@
       <c r="A133" s="71" t="n">
         <v>129</v>
       </c>
-      <c r="B133" s="72" t="inlineStr">
-        <is>
-          <t>1784313900065</t>
-        </is>
-      </c>
+      <c r="B133" s="72" t="n"/>
       <c r="C133" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -25662,7 +25251,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>/composition/layers/65/clips/1/connect</t>
+          <t>/composition/layers/65/connectnextclip</t>
         </is>
       </c>
       <c r="M133" s="71" t="n">
@@ -25688,7 +25277,7 @@
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>/composition/layers/65/clips/1/connect</t>
+          <t>/composition/layers/65/connectnextclip</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
@@ -25711,11 +25300,7 @@
       <c r="A134" s="71" t="n">
         <v>130</v>
       </c>
-      <c r="B134" s="72" t="inlineStr">
-        <is>
-          <t>1784313900119</t>
-        </is>
-      </c>
+      <c r="B134" s="72" t="n"/>
       <c r="C134" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -25757,7 +25342,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>/composition/layers/119/clips/1/connect</t>
+          <t>/composition/layers/119/connectnextclip</t>
         </is>
       </c>
       <c r="M134" s="71" t="n">
@@ -25783,7 +25368,7 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>/composition/layers/119/clips/1/connect</t>
+          <t>/composition/layers/119/connectnextclip</t>
         </is>
       </c>
       <c r="V134" t="inlineStr">
@@ -25806,11 +25391,7 @@
       <c r="A135" s="71" t="n">
         <v>131</v>
       </c>
-      <c r="B135" s="72" t="inlineStr">
-        <is>
-          <t>1784313901096</t>
-        </is>
-      </c>
+      <c r="B135" s="72" t="n"/>
       <c r="C135" t="inlineStr">
         <is>
           <t>wake</t>
@@ -25886,11 +25467,7 @@
       <c r="A136" s="71" t="n">
         <v>132</v>
       </c>
-      <c r="B136" s="72" t="inlineStr">
-        <is>
-          <t>1784313900096</t>
-        </is>
-      </c>
+      <c r="B136" s="72" t="n"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -25932,7 +25509,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>/composition/layers/96/clips/1/video/opacity</t>
+          <t>/composition/layers/96/clips/1/connect</t>
         </is>
       </c>
       <c r="M136" s="71" t="n">
@@ -25962,7 +25539,12 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>/composition/layers/96/clips/1/video/opacity</t>
+          <t>/composition/layers/96/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -25970,11 +25552,7 @@
       <c r="A137" s="71" t="n">
         <v>133</v>
       </c>
-      <c r="B137" s="72" t="inlineStr">
-        <is>
-          <t>1784313902096</t>
-        </is>
-      </c>
+      <c r="B137" s="72" t="n"/>
       <c r="C137" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -26016,7 +25594,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>/composition/layers/96/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/96/clips/1/connect</t>
         </is>
       </c>
       <c r="M137" s="71" t="n">
@@ -26046,7 +25624,12 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>/composition/layers/96/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/96/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -26054,11 +25637,7 @@
       <c r="A138" s="71" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="72" t="inlineStr">
-        <is>
-          <t>1784313901112</t>
-        </is>
-      </c>
+      <c r="B138" s="72" t="n"/>
       <c r="C138" t="inlineStr">
         <is>
           <t>wake</t>
@@ -26134,11 +25713,7 @@
       <c r="A139" s="71" t="n">
         <v>135</v>
       </c>
-      <c r="B139" s="72" t="inlineStr">
-        <is>
-          <t>1784313900112</t>
-        </is>
-      </c>
+      <c r="B139" s="72" t="n"/>
       <c r="C139" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -26180,7 +25755,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>/composition/layers/112/clips/1/video/opacity</t>
+          <t>/composition/layers/112/clips/1/connect</t>
         </is>
       </c>
       <c r="M139" s="71" t="n">
@@ -26210,7 +25785,12 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>/composition/layers/112/clips/1/video/opacity</t>
+          <t>/composition/layers/112/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -26218,11 +25798,7 @@
       <c r="A140" s="71" t="n">
         <v>136</v>
       </c>
-      <c r="B140" s="72" t="inlineStr">
-        <is>
-          <t>1784313902112</t>
-        </is>
-      </c>
+      <c r="B140" s="72" t="n"/>
       <c r="C140" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -26264,7 +25840,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>/composition/layers/112/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/112/clips/1/connect</t>
         </is>
       </c>
       <c r="M140" s="71" t="n">
@@ -26294,7 +25870,12 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>/composition/layers/112/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/112/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -26302,11 +25883,7 @@
       <c r="A141" s="71" t="n">
         <v>137</v>
       </c>
-      <c r="B141" s="72" t="inlineStr">
-        <is>
-          <t>1784313901095</t>
-        </is>
-      </c>
+      <c r="B141" s="72" t="n"/>
       <c r="C141" t="inlineStr">
         <is>
           <t>wake</t>
@@ -26382,11 +25959,7 @@
       <c r="A142" s="71" t="n">
         <v>138</v>
       </c>
-      <c r="B142" s="72" t="inlineStr">
-        <is>
-          <t>1784313900095</t>
-        </is>
-      </c>
+      <c r="B142" s="72" t="n"/>
       <c r="C142" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -26428,7 +26001,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>/composition/layers/95/clips/1/video/opacity</t>
+          <t>/composition/layers/95/clips/1/connect</t>
         </is>
       </c>
       <c r="M142" s="71" t="n">
@@ -26458,7 +26031,12 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>/composition/layers/95/clips/1/video/opacity</t>
+          <t>/composition/layers/95/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -26466,11 +26044,7 @@
       <c r="A143" s="71" t="n">
         <v>139</v>
       </c>
-      <c r="B143" s="72" t="inlineStr">
-        <is>
-          <t>1784313902095</t>
-        </is>
-      </c>
+      <c r="B143" s="72" t="n"/>
       <c r="C143" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -26512,7 +26086,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>/composition/layers/95/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/95/clips/1/connect</t>
         </is>
       </c>
       <c r="M143" s="71" t="n">
@@ -26542,7 +26116,12 @@
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>/composition/layers/95/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/95/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -26550,11 +26129,7 @@
       <c r="A144" s="71" t="n">
         <v>140</v>
       </c>
-      <c r="B144" s="72" t="inlineStr">
-        <is>
-          <t>1784313900125</t>
-        </is>
-      </c>
+      <c r="B144" s="72" t="n"/>
       <c r="C144" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -26596,7 +26171,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>/composition/layers/125/clips/1/connect</t>
+          <t>/composition/layers/125/connectnextclip</t>
         </is>
       </c>
       <c r="M144" s="71" t="n">
@@ -26622,7 +26197,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>/composition/layers/125/clips/1/connect</t>
+          <t>/composition/layers/125/connectnextclip</t>
         </is>
       </c>
       <c r="V144" t="inlineStr">
@@ -26645,11 +26220,7 @@
       <c r="A145" s="71" t="n">
         <v>141</v>
       </c>
-      <c r="B145" s="72" t="inlineStr">
-        <is>
-          <t>1784313900088</t>
-        </is>
-      </c>
+      <c r="B145" s="72" t="n"/>
       <c r="C145" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -26691,7 +26262,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>/composition/layers/88/clips/1/connect</t>
+          <t>/composition/layers/88/connectnextclip</t>
         </is>
       </c>
       <c r="M145" s="71" t="n">
@@ -26717,7 +26288,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>/composition/layers/88/clips/1/connect</t>
+          <t>/composition/layers/88/connectnextclip</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
@@ -26740,11 +26311,7 @@
       <c r="A146" s="71" t="n">
         <v>142</v>
       </c>
-      <c r="B146" s="72" t="inlineStr">
-        <is>
-          <t>1784313900068</t>
-        </is>
-      </c>
+      <c r="B146" s="72" t="n"/>
       <c r="C146" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -26786,7 +26353,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>/composition/layers/68/clips/1/connect</t>
+          <t>/composition/layers/68/connectnextclip</t>
         </is>
       </c>
       <c r="M146" s="71" t="n">
@@ -26812,7 +26379,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>/composition/layers/68/clips/1/connect</t>
+          <t>/composition/layers/68/connectnextclip</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
@@ -26835,11 +26402,7 @@
       <c r="A147" s="71" t="n">
         <v>143</v>
       </c>
-      <c r="B147" s="72" t="inlineStr">
-        <is>
-          <t>1784313900081</t>
-        </is>
-      </c>
+      <c r="B147" s="72" t="n"/>
       <c r="C147" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -26881,7 +26444,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>/composition/layers/81/clips/1/connect</t>
+          <t>/composition/layers/81/connectnextclip</t>
         </is>
       </c>
       <c r="M147" s="71" t="n">
@@ -26907,7 +26470,7 @@
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>/composition/layers/81/clips/1/connect</t>
+          <t>/composition/layers/81/connectnextclip</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
@@ -26930,11 +26493,7 @@
       <c r="A148" s="71" t="n">
         <v>144</v>
       </c>
-      <c r="B148" s="72" t="inlineStr">
-        <is>
-          <t>1784313900084</t>
-        </is>
-      </c>
+      <c r="B148" s="72" t="n"/>
       <c r="C148" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -26976,7 +26535,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>/composition/layers/84/clips/1/connect</t>
+          <t>/composition/layers/84/connectnextclip</t>
         </is>
       </c>
       <c r="M148" s="71" t="n">
@@ -27002,7 +26561,7 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>/composition/layers/84/clips/1/connect</t>
+          <t>/composition/layers/84/connectnextclip</t>
         </is>
       </c>
       <c r="V148" t="inlineStr">
@@ -27025,11 +26584,7 @@
       <c r="A149" s="71" t="n">
         <v>145</v>
       </c>
-      <c r="B149" s="72" t="inlineStr">
-        <is>
-          <t>1784313900089</t>
-        </is>
-      </c>
+      <c r="B149" s="72" t="n"/>
       <c r="C149" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -27071,7 +26626,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>/composition/layers/89/clips/1/connect</t>
+          <t>/composition/layers/89/connectnextclip</t>
         </is>
       </c>
       <c r="M149" s="71" t="n">
@@ -27097,7 +26652,7 @@
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>/composition/layers/89/clips/1/connect</t>
+          <t>/composition/layers/89/connectnextclip</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
@@ -27120,11 +26675,7 @@
       <c r="A150" s="71" t="n">
         <v>146</v>
       </c>
-      <c r="B150" s="72" t="inlineStr">
-        <is>
-          <t>1784313900074</t>
-        </is>
-      </c>
+      <c r="B150" s="72" t="n"/>
       <c r="C150" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -27166,7 +26717,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>/composition/layers/74/clips/1/connect</t>
+          <t>/composition/layers/74/connectnextclip</t>
         </is>
       </c>
       <c r="M150" s="71" t="n">
@@ -27192,7 +26743,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>/composition/layers/74/clips/1/connect</t>
+          <t>/composition/layers/74/connectnextclip</t>
         </is>
       </c>
       <c r="V150" t="inlineStr">
@@ -27215,11 +26766,7 @@
       <c r="A151" s="71" t="n">
         <v>147</v>
       </c>
-      <c r="B151" s="72" t="inlineStr">
-        <is>
-          <t>1784313900076</t>
-        </is>
-      </c>
+      <c r="B151" s="72" t="n"/>
       <c r="C151" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -27261,7 +26808,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>/composition/layers/76/clips/1/connect</t>
+          <t>/composition/layers/76/connectnextclip</t>
         </is>
       </c>
       <c r="M151" s="71" t="n">
@@ -27287,7 +26834,7 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>/composition/layers/76/clips/1/connect</t>
+          <t>/composition/layers/76/connectnextclip</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
@@ -27310,11 +26857,7 @@
       <c r="A152" s="71" t="n">
         <v>148</v>
       </c>
-      <c r="B152" s="72" t="inlineStr">
-        <is>
-          <t>1784313900127</t>
-        </is>
-      </c>
+      <c r="B152" s="72" t="n"/>
       <c r="C152" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -27356,7 +26899,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>/composition/layers/127/clips/1/connect</t>
+          <t>/composition/layers/127/connectnextclip</t>
         </is>
       </c>
       <c r="M152" s="71" t="n">
@@ -27382,7 +26925,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>/composition/layers/127/clips/1/connect</t>
+          <t>/composition/layers/127/connectnextclip</t>
         </is>
       </c>
       <c r="V152" t="inlineStr">
@@ -27405,11 +26948,7 @@
       <c r="A153" s="71" t="n">
         <v>149</v>
       </c>
-      <c r="B153" s="72" t="inlineStr">
-        <is>
-          <t>1784313901116</t>
-        </is>
-      </c>
+      <c r="B153" s="72" t="n"/>
       <c r="C153" t="inlineStr">
         <is>
           <t>wake</t>
@@ -27485,11 +27024,7 @@
       <c r="A154" s="71" t="n">
         <v>150</v>
       </c>
-      <c r="B154" s="72" t="inlineStr">
-        <is>
-          <t>1784313900116</t>
-        </is>
-      </c>
+      <c r="B154" s="72" t="n"/>
       <c r="C154" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -27531,7 +27066,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>/composition/layers/116/clips/1/video/opacity</t>
+          <t>/composition/layers/116/clips/1/connect</t>
         </is>
       </c>
       <c r="M154" s="71" t="n">
@@ -27561,7 +27096,12 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>/composition/layers/116/clips/1/video/opacity</t>
+          <t>/composition/layers/116/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -27569,11 +27109,7 @@
       <c r="A155" s="71" t="n">
         <v>151</v>
       </c>
-      <c r="B155" s="72" t="inlineStr">
-        <is>
-          <t>1784313902116</t>
-        </is>
-      </c>
+      <c r="B155" s="72" t="n"/>
       <c r="C155" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -27615,7 +27151,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>/composition/layers/116/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/116/clips/1/connect</t>
         </is>
       </c>
       <c r="M155" s="71" t="n">
@@ -27645,7 +27181,12 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>/composition/layers/116/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/116/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -27653,11 +27194,7 @@
       <c r="A156" s="71" t="n">
         <v>152</v>
       </c>
-      <c r="B156" s="72" t="inlineStr">
-        <is>
-          <t>1784313900124</t>
-        </is>
-      </c>
+      <c r="B156" s="72" t="n"/>
       <c r="C156" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -27699,7 +27236,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>/composition/layers/124/clips/1/connect</t>
+          <t>/composition/layers/124/connectnextclip</t>
         </is>
       </c>
       <c r="M156" s="71" t="n">
@@ -27725,7 +27262,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>/composition/layers/124/clips/1/connect</t>
+          <t>/composition/layers/124/connectnextclip</t>
         </is>
       </c>
       <c r="V156" t="inlineStr">
@@ -27748,11 +27285,7 @@
       <c r="A157" s="71" t="n">
         <v>153</v>
       </c>
-      <c r="B157" s="72" t="inlineStr">
-        <is>
-          <t>1784313901115</t>
-        </is>
-      </c>
+      <c r="B157" s="72" t="n"/>
       <c r="C157" t="inlineStr">
         <is>
           <t>wake</t>
@@ -27828,11 +27361,7 @@
       <c r="A158" s="71" t="n">
         <v>154</v>
       </c>
-      <c r="B158" s="72" t="inlineStr">
-        <is>
-          <t>1784313900115</t>
-        </is>
-      </c>
+      <c r="B158" s="72" t="n"/>
       <c r="C158" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -27874,7 +27403,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>/composition/layers/115/clips/1/video/opacity</t>
+          <t>/composition/layers/115/clips/1/connect</t>
         </is>
       </c>
       <c r="M158" s="71" t="n">
@@ -27904,7 +27433,12 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>/composition/layers/115/clips/1/video/opacity</t>
+          <t>/composition/layers/115/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -27912,11 +27446,7 @@
       <c r="A159" s="71" t="n">
         <v>155</v>
       </c>
-      <c r="B159" s="72" t="inlineStr">
-        <is>
-          <t>1784313902115</t>
-        </is>
-      </c>
+      <c r="B159" s="72" t="n"/>
       <c r="C159" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -27958,7 +27488,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>/composition/layers/115/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/115/clips/1/connect</t>
         </is>
       </c>
       <c r="M159" s="71" t="n">
@@ -27988,7 +27518,12 @@
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>/composition/layers/115/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/115/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -27996,11 +27531,7 @@
       <c r="A160" s="71" t="n">
         <v>156</v>
       </c>
-      <c r="B160" s="72" t="inlineStr">
-        <is>
-          <t>1784313900093</t>
-        </is>
-      </c>
+      <c r="B160" s="72" t="n"/>
       <c r="C160" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -28042,7 +27573,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>/composition/layers/93/clips/1/connect</t>
+          <t>/composition/layers/93/connectnextclip</t>
         </is>
       </c>
       <c r="M160" s="71" t="n">
@@ -28068,7 +27599,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>/composition/layers/93/clips/1/connect</t>
+          <t>/composition/layers/93/connectnextclip</t>
         </is>
       </c>
       <c r="V160" t="inlineStr">
@@ -28091,11 +27622,7 @@
       <c r="A161" s="71" t="n">
         <v>157</v>
       </c>
-      <c r="B161" s="72" t="inlineStr">
-        <is>
-          <t>1784313901097</t>
-        </is>
-      </c>
+      <c r="B161" s="72" t="n"/>
       <c r="C161" t="inlineStr">
         <is>
           <t>wake</t>
@@ -28171,11 +27698,7 @@
       <c r="A162" s="71" t="n">
         <v>158</v>
       </c>
-      <c r="B162" s="72" t="inlineStr">
-        <is>
-          <t>1784313900097</t>
-        </is>
-      </c>
+      <c r="B162" s="72" t="n"/>
       <c r="C162" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -28217,7 +27740,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>/composition/layers/97/clips/1/video/opacity</t>
+          <t>/composition/layers/97/clips/1/connect</t>
         </is>
       </c>
       <c r="M162" s="71" t="n">
@@ -28247,7 +27770,12 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>/composition/layers/97/clips/1/video/opacity</t>
+          <t>/composition/layers/97/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28255,11 +27783,7 @@
       <c r="A163" s="71" t="n">
         <v>159</v>
       </c>
-      <c r="B163" s="72" t="inlineStr">
-        <is>
-          <t>1784313902097</t>
-        </is>
-      </c>
+      <c r="B163" s="72" t="n"/>
       <c r="C163" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -28301,7 +27825,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>/composition/layers/97/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/97/clips/1/connect</t>
         </is>
       </c>
       <c r="M163" s="71" t="n">
@@ -28331,7 +27855,12 @@
       </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>/composition/layers/97/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/97/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28339,11 +27868,7 @@
       <c r="A164" s="71" t="n">
         <v>160</v>
       </c>
-      <c r="B164" s="72" t="inlineStr">
-        <is>
-          <t>1784313901102</t>
-        </is>
-      </c>
+      <c r="B164" s="72" t="n"/>
       <c r="C164" t="inlineStr">
         <is>
           <t>wake</t>
@@ -28419,11 +27944,7 @@
       <c r="A165" s="71" t="n">
         <v>161</v>
       </c>
-      <c r="B165" s="72" t="inlineStr">
-        <is>
-          <t>1784313900102</t>
-        </is>
-      </c>
+      <c r="B165" s="72" t="n"/>
       <c r="C165" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -28465,7 +27986,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>/composition/layers/102/clips/1/video/opacity</t>
+          <t>/composition/layers/102/clips/1/connect</t>
         </is>
       </c>
       <c r="M165" s="71" t="n">
@@ -28495,7 +28016,12 @@
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>/composition/layers/102/clips/1/video/opacity</t>
+          <t>/composition/layers/102/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28503,11 +28029,7 @@
       <c r="A166" s="71" t="n">
         <v>162</v>
       </c>
-      <c r="B166" s="72" t="inlineStr">
-        <is>
-          <t>1784313902102</t>
-        </is>
-      </c>
+      <c r="B166" s="72" t="n"/>
       <c r="C166" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -28549,7 +28071,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>/composition/layers/102/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/102/clips/1/connect</t>
         </is>
       </c>
       <c r="M166" s="71" t="n">
@@ -28579,7 +28101,12 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>/composition/layers/102/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/102/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28587,11 +28114,7 @@
       <c r="A167" s="71" t="n">
         <v>163</v>
       </c>
-      <c r="B167" s="72" t="inlineStr">
-        <is>
-          <t>1784313901101</t>
-        </is>
-      </c>
+      <c r="B167" s="72" t="n"/>
       <c r="C167" t="inlineStr">
         <is>
           <t>wake</t>
@@ -28667,11 +28190,7 @@
       <c r="A168" s="71" t="n">
         <v>164</v>
       </c>
-      <c r="B168" s="72" t="inlineStr">
-        <is>
-          <t>1784313900101</t>
-        </is>
-      </c>
+      <c r="B168" s="72" t="n"/>
       <c r="C168" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -28713,7 +28232,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>/composition/layers/101/clips/1/video/opacity</t>
+          <t>/composition/layers/101/clips/1/connect</t>
         </is>
       </c>
       <c r="M168" s="71" t="n">
@@ -28743,7 +28262,12 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>/composition/layers/101/clips/1/video/opacity</t>
+          <t>/composition/layers/101/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28751,11 +28275,7 @@
       <c r="A169" s="71" t="n">
         <v>165</v>
       </c>
-      <c r="B169" s="72" t="inlineStr">
-        <is>
-          <t>1784313902101</t>
-        </is>
-      </c>
+      <c r="B169" s="72" t="n"/>
       <c r="C169" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -28797,7 +28317,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>/composition/layers/101/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/101/clips/1/connect</t>
         </is>
       </c>
       <c r="M169" s="71" t="n">
@@ -28827,7 +28347,12 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>/composition/layers/101/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/101/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28835,11 +28360,7 @@
       <c r="A170" s="71" t="n">
         <v>166</v>
       </c>
-      <c r="B170" s="72" t="inlineStr">
-        <is>
-          <t>1784313901098</t>
-        </is>
-      </c>
+      <c r="B170" s="72" t="n"/>
       <c r="C170" t="inlineStr">
         <is>
           <t>wake</t>
@@ -28915,11 +28436,7 @@
       <c r="A171" s="71" t="n">
         <v>167</v>
       </c>
-      <c r="B171" s="72" t="inlineStr">
-        <is>
-          <t>1784313900098</t>
-        </is>
-      </c>
+      <c r="B171" s="72" t="n"/>
       <c r="C171" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -28961,7 +28478,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>/composition/layers/98/clips/1/video/opacity</t>
+          <t>/composition/layers/98/clips/1/connect</t>
         </is>
       </c>
       <c r="M171" s="71" t="n">
@@ -28991,7 +28508,12 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>/composition/layers/98/clips/1/video/opacity</t>
+          <t>/composition/layers/98/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -28999,11 +28521,7 @@
       <c r="A172" s="71" t="n">
         <v>168</v>
       </c>
-      <c r="B172" s="72" t="inlineStr">
-        <is>
-          <t>1784313902098</t>
-        </is>
-      </c>
+      <c r="B172" s="72" t="n"/>
       <c r="C172" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -29045,7 +28563,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>/composition/layers/98/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/98/clips/1/connect</t>
         </is>
       </c>
       <c r="M172" s="71" t="n">
@@ -29075,7 +28593,12 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>/composition/layers/98/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/98/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -29083,11 +28606,7 @@
       <c r="A173" s="71" t="n">
         <v>169</v>
       </c>
-      <c r="B173" s="72" t="inlineStr">
-        <is>
-          <t>1784313901107</t>
-        </is>
-      </c>
+      <c r="B173" s="72" t="n"/>
       <c r="C173" t="inlineStr">
         <is>
           <t>wake</t>
@@ -29163,11 +28682,7 @@
       <c r="A174" s="71" t="n">
         <v>170</v>
       </c>
-      <c r="B174" s="72" t="inlineStr">
-        <is>
-          <t>1784313900107</t>
-        </is>
-      </c>
+      <c r="B174" s="72" t="n"/>
       <c r="C174" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -29209,7 +28724,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>/composition/layers/107/clips/1/video/opacity</t>
+          <t>/composition/layers/107/clips/1/connect</t>
         </is>
       </c>
       <c r="M174" s="71" t="n">
@@ -29239,7 +28754,12 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>/composition/layers/107/clips/1/video/opacity</t>
+          <t>/composition/layers/107/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -29247,11 +28767,7 @@
       <c r="A175" s="71" t="n">
         <v>171</v>
       </c>
-      <c r="B175" s="72" t="inlineStr">
-        <is>
-          <t>1784313902107</t>
-        </is>
-      </c>
+      <c r="B175" s="72" t="n"/>
       <c r="C175" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -29293,7 +28809,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>/composition/layers/107/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/107/clips/1/connect</t>
         </is>
       </c>
       <c r="M175" s="71" t="n">
@@ -29323,7 +28839,12 @@
       </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>/composition/layers/107/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/107/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -29331,11 +28852,7 @@
       <c r="A176" s="71" t="n">
         <v>172</v>
       </c>
-      <c r="B176" s="72" t="inlineStr">
-        <is>
-          <t>1784313900130</t>
-        </is>
-      </c>
+      <c r="B176" s="72" t="n"/>
       <c r="C176" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -29377,7 +28894,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>/composition/layers/130/clips/1/connect</t>
+          <t>/composition/layers/130/connectnextclip</t>
         </is>
       </c>
       <c r="M176" s="71" t="n">
@@ -29403,7 +28920,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>/composition/layers/130/clips/1/connect</t>
+          <t>/composition/layers/130/connectnextclip</t>
         </is>
       </c>
       <c r="V176" t="inlineStr">
@@ -29426,11 +28943,7 @@
       <c r="A177" s="71" t="n">
         <v>173</v>
       </c>
-      <c r="B177" s="72" t="inlineStr">
-        <is>
-          <t>1784313900121</t>
-        </is>
-      </c>
+      <c r="B177" s="72" t="n"/>
       <c r="C177" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -29472,7 +28985,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>/composition/layers/121/clips/1/connect</t>
+          <t>/composition/layers/121/connectnextclip</t>
         </is>
       </c>
       <c r="M177" s="71" t="n">
@@ -29498,7 +29011,7 @@
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>/composition/layers/121/clips/1/connect</t>
+          <t>/composition/layers/121/connectnextclip</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
@@ -29521,11 +29034,7 @@
       <c r="A178" s="71" t="n">
         <v>174</v>
       </c>
-      <c r="B178" s="72" t="inlineStr">
-        <is>
-          <t>1784313901111</t>
-        </is>
-      </c>
+      <c r="B178" s="72" t="n"/>
       <c r="C178" t="inlineStr">
         <is>
           <t>wake</t>
@@ -29601,11 +29110,7 @@
       <c r="A179" s="71" t="n">
         <v>175</v>
       </c>
-      <c r="B179" s="72" t="inlineStr">
-        <is>
-          <t>1784313900111</t>
-        </is>
-      </c>
+      <c r="B179" s="72" t="n"/>
       <c r="C179" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -29647,7 +29152,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>/composition/layers/111/clips/1/video/opacity</t>
+          <t>/composition/layers/111/clips/1/connect</t>
         </is>
       </c>
       <c r="M179" s="71" t="n">
@@ -29677,7 +29182,12 @@
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>/composition/layers/111/clips/1/video/opacity</t>
+          <t>/composition/layers/111/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -29685,11 +29195,7 @@
       <c r="A180" s="71" t="n">
         <v>176</v>
       </c>
-      <c r="B180" s="72" t="inlineStr">
-        <is>
-          <t>1784313902111</t>
-        </is>
-      </c>
+      <c r="B180" s="72" t="n"/>
       <c r="C180" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -29731,7 +29237,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>/composition/layers/111/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/111/clips/1/connect</t>
         </is>
       </c>
       <c r="M180" s="71" t="n">
@@ -29761,7 +29267,12 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>/composition/layers/111/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/111/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -29769,11 +29280,7 @@
       <c r="A181" s="71" t="n">
         <v>177</v>
       </c>
-      <c r="B181" s="72" t="inlineStr">
-        <is>
-          <t>1784313900128</t>
-        </is>
-      </c>
+      <c r="B181" s="72" t="n"/>
       <c r="C181" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -29815,7 +29322,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>/composition/layers/128/clips/1/connect</t>
+          <t>/composition/layers/128/connectnextclip</t>
         </is>
       </c>
       <c r="M181" s="71" t="n">
@@ -29841,7 +29348,7 @@
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>/composition/layers/128/clips/1/connect</t>
+          <t>/composition/layers/128/connectnextclip</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
@@ -29864,11 +29371,7 @@
       <c r="A182" s="71" t="n">
         <v>178</v>
       </c>
-      <c r="B182" s="72" t="inlineStr">
-        <is>
-          <t>1784313901110</t>
-        </is>
-      </c>
+      <c r="B182" s="72" t="n"/>
       <c r="C182" t="inlineStr">
         <is>
           <t>wake</t>
@@ -29944,11 +29447,7 @@
       <c r="A183" s="71" t="n">
         <v>179</v>
       </c>
-      <c r="B183" s="72" t="inlineStr">
-        <is>
-          <t>1784313900110</t>
-        </is>
-      </c>
+      <c r="B183" s="72" t="n"/>
       <c r="C183" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -29990,7 +29489,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>/composition/layers/110/clips/1/video/opacity</t>
+          <t>/composition/layers/110/clips/1/connect</t>
         </is>
       </c>
       <c r="M183" s="71" t="n">
@@ -30020,7 +29519,12 @@
       </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>/composition/layers/110/clips/1/video/opacity</t>
+          <t>/composition/layers/110/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -30028,11 +29532,7 @@
       <c r="A184" s="71" t="n">
         <v>180</v>
       </c>
-      <c r="B184" s="72" t="inlineStr">
-        <is>
-          <t>1784313902110</t>
-        </is>
-      </c>
+      <c r="B184" s="72" t="n"/>
       <c r="C184" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -30074,7 +29574,7 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>/composition/layers/110/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/110/clips/1/connect</t>
         </is>
       </c>
       <c r="M184" s="71" t="n">
@@ -30104,7 +29604,12 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>/composition/layers/110/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/110/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -30112,11 +29617,7 @@
       <c r="A185" s="71" t="n">
         <v>181</v>
       </c>
-      <c r="B185" s="72" t="inlineStr">
-        <is>
-          <t>1784313900131</t>
-        </is>
-      </c>
+      <c r="B185" s="72" t="n"/>
       <c r="C185" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -30158,7 +29659,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>/composition/layers/131/clips/1/connect</t>
+          <t>/composition/layers/131/connectnextclip</t>
         </is>
       </c>
       <c r="M185" s="71" t="n">
@@ -30184,7 +29685,7 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>/composition/layers/131/clips/1/connect</t>
+          <t>/composition/layers/131/connectnextclip</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
@@ -30207,11 +29708,7 @@
       <c r="A186" s="71" t="n">
         <v>182</v>
       </c>
-      <c r="B186" s="72" t="inlineStr">
-        <is>
-          <t>1784313901105</t>
-        </is>
-      </c>
+      <c r="B186" s="72" t="n"/>
       <c r="C186" t="inlineStr">
         <is>
           <t>wake</t>
@@ -30287,11 +29784,7 @@
       <c r="A187" s="71" t="n">
         <v>183</v>
       </c>
-      <c r="B187" s="72" t="inlineStr">
-        <is>
-          <t>1784313900105</t>
-        </is>
-      </c>
+      <c r="B187" s="72" t="n"/>
       <c r="C187" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -30333,7 +29826,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>/composition/layers/105/clips/1/video/opacity</t>
+          <t>/composition/layers/105/clips/1/connect</t>
         </is>
       </c>
       <c r="M187" s="71" t="n">
@@ -30363,7 +29856,12 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>/composition/layers/105/clips/1/video/opacity</t>
+          <t>/composition/layers/105/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -30371,11 +29869,7 @@
       <c r="A188" s="71" t="n">
         <v>184</v>
       </c>
-      <c r="B188" s="72" t="inlineStr">
-        <is>
-          <t>1784313902105</t>
-        </is>
-      </c>
+      <c r="B188" s="72" t="n"/>
       <c r="C188" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -30417,7 +29911,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>/composition/layers/105/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/105/clips/1/connect</t>
         </is>
       </c>
       <c r="M188" s="71" t="n">
@@ -30447,7 +29941,12 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>/composition/layers/105/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/105/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X188" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -30455,11 +29954,7 @@
       <c r="A189" s="71" t="n">
         <v>185</v>
       </c>
-      <c r="B189" s="72" t="inlineStr">
-        <is>
-          <t>1784313901117</t>
-        </is>
-      </c>
+      <c r="B189" s="72" t="n"/>
       <c r="C189" t="inlineStr">
         <is>
           <t>wake</t>
@@ -30535,11 +30030,7 @@
       <c r="A190" s="71" t="n">
         <v>186</v>
       </c>
-      <c r="B190" s="72" t="inlineStr">
-        <is>
-          <t>1784313900117</t>
-        </is>
-      </c>
+      <c r="B190" s="72" t="n"/>
       <c r="C190" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -30581,7 +30072,7 @@
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>/composition/layers/117/clips/1/video/opacity</t>
+          <t>/composition/layers/117/clips/1/connect</t>
         </is>
       </c>
       <c r="M190" s="71" t="n">
@@ -30611,7 +30102,12 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>/composition/layers/117/clips/1/video/opacity</t>
+          <t>/composition/layers/117/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X190" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -30619,11 +30115,7 @@
       <c r="A191" s="71" t="n">
         <v>187</v>
       </c>
-      <c r="B191" s="72" t="inlineStr">
-        <is>
-          <t>1784313902117</t>
-        </is>
-      </c>
+      <c r="B191" s="72" t="n"/>
       <c r="C191" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -30665,7 +30157,7 @@
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>/composition/layers/117/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/117/clips/1/connect</t>
         </is>
       </c>
       <c r="M191" s="71" t="n">
@@ -30695,7 +30187,12 @@
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>/composition/layers/117/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/117/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X191" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -30703,11 +30200,7 @@
       <c r="A192" s="71" t="n">
         <v>188</v>
       </c>
-      <c r="B192" s="72" t="inlineStr">
-        <is>
-          <t>1784313900132</t>
-        </is>
-      </c>
+      <c r="B192" s="72" t="n"/>
       <c r="C192" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -30749,7 +30242,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>/composition/layers/132/clips/1/connect</t>
+          <t>/composition/layers/132/connectnextclip</t>
         </is>
       </c>
       <c r="M192" s="71" t="n">
@@ -30775,7 +30268,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>/composition/layers/132/clips/1/connect</t>
+          <t>/composition/layers/132/connectnextclip</t>
         </is>
       </c>
       <c r="V192" t="inlineStr">
@@ -30798,11 +30291,7 @@
       <c r="A193" s="71" t="n">
         <v>189</v>
       </c>
-      <c r="B193" s="72" t="inlineStr">
-        <is>
-          <t>1784313900134</t>
-        </is>
-      </c>
+      <c r="B193" s="72" t="n"/>
       <c r="C193" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -30844,7 +30333,7 @@
       </c>
       <c r="L193" t="inlineStr">
         <is>
-          <t>/composition/layers/134/clips/1/connect</t>
+          <t>/composition/layers/134/connectnextclip</t>
         </is>
       </c>
       <c r="M193" s="71" t="n">
@@ -30870,7 +30359,7 @@
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>/composition/layers/134/clips/1/connect</t>
+          <t>/composition/layers/134/connectnextclip</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
@@ -30893,11 +30382,7 @@
       <c r="A194" s="71" t="n">
         <v>190</v>
       </c>
-      <c r="B194" s="72" t="inlineStr">
-        <is>
-          <t>1784313900118</t>
-        </is>
-      </c>
+      <c r="B194" s="72" t="n"/>
       <c r="C194" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -30939,7 +30424,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>/composition/layers/118/clips/1/connect</t>
+          <t>/composition/layers/118/connectnextclip</t>
         </is>
       </c>
       <c r="M194" s="71" t="n">
@@ -30965,7 +30450,7 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>/composition/layers/118/clips/1/connect</t>
+          <t>/composition/layers/118/connectnextclip</t>
         </is>
       </c>
       <c r="V194" t="inlineStr">
@@ -30988,11 +30473,7 @@
       <c r="A195" s="71" t="n">
         <v>191</v>
       </c>
-      <c r="B195" s="72" t="inlineStr">
-        <is>
-          <t>1784313900133</t>
-        </is>
-      </c>
+      <c r="B195" s="72" t="n"/>
       <c r="C195" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -31034,7 +30515,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>/composition/layers/133/clips/1/connect</t>
+          <t>/composition/layers/133/connectnextclip</t>
         </is>
       </c>
       <c r="M195" s="71" t="n">
@@ -31060,7 +30541,7 @@
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>/composition/layers/133/clips/1/connect</t>
+          <t>/composition/layers/133/connectnextclip</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
@@ -31083,11 +30564,7 @@
       <c r="A196" s="71" t="n">
         <v>192</v>
       </c>
-      <c r="B196" s="72" t="inlineStr">
-        <is>
-          <t>1784313900129</t>
-        </is>
-      </c>
+      <c r="B196" s="72" t="n"/>
       <c r="C196" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -31129,7 +30606,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>/composition/layers/129/clips/1/connect</t>
+          <t>/composition/layers/129/connectnextclip</t>
         </is>
       </c>
       <c r="M196" s="71" t="n">
@@ -31155,7 +30632,7 @@
       </c>
       <c r="U196" t="inlineStr">
         <is>
-          <t>/composition/layers/129/clips/1/connect</t>
+          <t>/composition/layers/129/connectnextclip</t>
         </is>
       </c>
       <c r="V196" t="inlineStr">
@@ -31178,11 +30655,7 @@
       <c r="A197" s="71" t="n">
         <v>193</v>
       </c>
-      <c r="B197" s="72" t="inlineStr">
-        <is>
-          <t>1784313901103</t>
-        </is>
-      </c>
+      <c r="B197" s="72" t="n"/>
       <c r="C197" t="inlineStr">
         <is>
           <t>wake</t>
@@ -31258,11 +30731,7 @@
       <c r="A198" s="71" t="n">
         <v>194</v>
       </c>
-      <c r="B198" s="72" t="inlineStr">
-        <is>
-          <t>1784313900103</t>
-        </is>
-      </c>
+      <c r="B198" s="72" t="n"/>
       <c r="C198" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -31304,7 +30773,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>/composition/layers/103/clips/1/video/opacity</t>
+          <t>/composition/layers/103/clips/1/connect</t>
         </is>
       </c>
       <c r="M198" s="71" t="n">
@@ -31334,7 +30803,12 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>/composition/layers/103/clips/1/video/opacity</t>
+          <t>/composition/layers/103/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X198" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -31342,11 +30816,7 @@
       <c r="A199" s="71" t="n">
         <v>195</v>
       </c>
-      <c r="B199" s="72" t="inlineStr">
-        <is>
-          <t>1784313902103</t>
-        </is>
-      </c>
+      <c r="B199" s="72" t="n"/>
       <c r="C199" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -31388,7 +30858,7 @@
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>/composition/layers/103/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/103/clips/1/connect</t>
         </is>
       </c>
       <c r="M199" s="71" t="n">
@@ -31418,7 +30888,12 @@
       </c>
       <c r="U199" t="inlineStr">
         <is>
-          <t>/composition/layers/103/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/103/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -31426,11 +30901,7 @@
       <c r="A200" s="71" t="n">
         <v>196</v>
       </c>
-      <c r="B200" s="72" t="inlineStr">
-        <is>
-          <t>1784313900126</t>
-        </is>
-      </c>
+      <c r="B200" s="72" t="n"/>
       <c r="C200" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -31472,7 +30943,7 @@
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>/composition/layers/126/clips/1/connect</t>
+          <t>/composition/layers/126/connectnextclip</t>
         </is>
       </c>
       <c r="M200" s="71" t="n">
@@ -31498,7 +30969,7 @@
       </c>
       <c r="U200" t="inlineStr">
         <is>
-          <t>/composition/layers/126/clips/1/connect</t>
+          <t>/composition/layers/126/connectnextclip</t>
         </is>
       </c>
       <c r="V200" t="inlineStr">
@@ -31521,11 +30992,7 @@
       <c r="A201" s="71" t="n">
         <v>197</v>
       </c>
-      <c r="B201" s="72" t="inlineStr">
-        <is>
-          <t>1784313901108</t>
-        </is>
-      </c>
+      <c r="B201" s="72" t="n"/>
       <c r="C201" t="inlineStr">
         <is>
           <t>wake</t>
@@ -31601,11 +31068,7 @@
       <c r="A202" s="71" t="n">
         <v>198</v>
       </c>
-      <c r="B202" s="72" t="inlineStr">
-        <is>
-          <t>1784313900108</t>
-        </is>
-      </c>
+      <c r="B202" s="72" t="n"/>
       <c r="C202" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -31647,7 +31110,7 @@
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>/composition/layers/108/clips/1/video/opacity</t>
+          <t>/composition/layers/108/clips/1/connect</t>
         </is>
       </c>
       <c r="M202" s="71" t="n">
@@ -31677,7 +31140,12 @@
       </c>
       <c r="U202" t="inlineStr">
         <is>
-          <t>/composition/layers/108/clips/1/video/opacity</t>
+          <t>/composition/layers/108/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X202" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -31685,11 +31153,7 @@
       <c r="A203" s="71" t="n">
         <v>199</v>
       </c>
-      <c r="B203" s="72" t="inlineStr">
-        <is>
-          <t>1784313902108</t>
-        </is>
-      </c>
+      <c r="B203" s="72" t="n"/>
       <c r="C203" t="inlineStr">
         <is>
           <t>motion_rotation</t>
@@ -31731,7 +31195,7 @@
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>/composition/layers/108/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/108/clips/1/connect</t>
         </is>
       </c>
       <c r="M203" s="71" t="n">
@@ -31761,7 +31225,12 @@
       </c>
       <c r="U203" t="inlineStr">
         <is>
-          <t>/composition/layers/108/clips/1/video/effects/transform/rotationz</t>
+          <t>/composition/layers/108/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -31769,11 +31238,7 @@
       <c r="A204" s="71" t="n">
         <v>200</v>
       </c>
-      <c r="B204" s="72" t="inlineStr">
-        <is>
-          <t>1784313901100</t>
-        </is>
-      </c>
+      <c r="B204" s="72" t="n"/>
       <c r="C204" t="inlineStr">
         <is>
           <t>wake</t>
@@ -31849,11 +31314,7 @@
       <c r="A205" s="71" t="n">
         <v>201</v>
       </c>
-      <c r="B205" s="72" t="inlineStr">
-        <is>
-          <t>1784313900100</t>
-        </is>
-      </c>
+      <c r="B205" s="72" t="n"/>
       <c r="C205" t="inlineStr">
         <is>
           <t>opacity</t>
@@ -31895,7 +31356,7 @@
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>/composition/layers/100/clips/1/video/opacity</t>
+          <t>/composition/layers/100/clips/1/connect</t>
         </is>
       </c>
       <c r="M205" s="71" t="n">
@@ -31925,7 +31386,12 @@
       </c>
       <c r="U205" t="inlineStr">
         <is>
-          <t>/composition/layers/100/clips/1/video/opacity</t>
+          <t>/composition/layers/100/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X205" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -31933,11 +31399,7 @@
       <c r="A206" s="71" t="n">
         <v>202</v>
       </c>
-      <c r="B206" s="72" t="inlineStr">
-        <is>
-          <t>1784313902100</t>
-        </is>
-      </c>
+      <c r="B206" s="72" t="n"/>
       <c r="C206" t="inlineStr">
         <is>
           <t>motion_y</t>
@@ -31979,7 +31441,7 @@
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>/composition/layers/100/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/100/clips/1/connect</t>
         </is>
       </c>
       <c r="M206" s="71" t="n">
@@ -32009,7 +31471,12 @@
       </c>
       <c r="U206" t="inlineStr">
         <is>
-          <t>/composition/layers/100/clips/1/video/effects/transform/positiony</t>
+          <t>/composition/layers/100/clips/1/connect</t>
+        </is>
+      </c>
+      <c r="X206" t="inlineStr">
+        <is>
+          <t>Disconnected=1</t>
         </is>
       </c>
     </row>
@@ -32017,11 +31484,7 @@
       <c r="A207" s="71" t="n">
         <v>203</v>
       </c>
-      <c r="B207" s="72" t="inlineStr">
-        <is>
-          <t>1784313900123</t>
-        </is>
-      </c>
+      <c r="B207" s="72" t="n"/>
       <c r="C207" t="inlineStr">
         <is>
           <t>button_connect</t>
@@ -32063,7 +31526,7 @@
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>/composition/layers/123/clips/1/connect</t>
+          <t>/composition/layers/123/connectnextclip</t>
         </is>
       </c>
       <c r="M207" s="71" t="n">
@@ -32089,7 +31552,7 @@
       </c>
       <c r="U207" t="inlineStr">
         <is>
-          <t>/composition/layers/123/clips/1/connect</t>
+          <t>/composition/layers/123/connectnextclip</t>
         </is>
       </c>
       <c r="V207" t="inlineStr">
